--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0017.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0017.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Một Resonator trong đội hiện tại đang sử dụng vũ khí hoặc Echoes có sẵn dữ liệu thử thách. Hệ thống sẽ sử dụng đội hình gốc cho thử thách. Tiếp tục?</t>
+          <t>Một Resonator trong đội hiện tại đang sử dụng vũ khí hoặc Echo có sẵn dữ liệu thử thách. Hệ thống sẽ sử dụng đội hình gốc cho thử thách. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 4 Thẻ Novelty.&lt;/color&gt;</t>
         </is>
       </c>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 4 lá Vật phẩm Đặc biệt.&lt;/color&gt;</t>
         </is>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 6 lá Fusion.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 6 lá Fusion.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 6 lá Electro.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 6 lá Electro.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 6 thẻ Aero.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 6 lá Aero.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 8 lá có Chi phí 3.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 8 lá có Chi phí 3.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Activated)&lt;/color&gt;
+          <t>Yêu Cầu Kích Hoạt &lt;color=#32dbb1&gt;(Đã kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsActivate.T_IconTipsActivate/&gt;&lt;color=#32dbb1&gt;Bộ bài của bạn phải chứa ít nhất 3 Thẻ Novelty.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Unactivated)&lt;/color&gt;
+          <t>Yêu cầu kích hoạt &lt;color=#fc6464&gt;(Chưa kích hoạt)&lt;/color&gt;
 &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/SoundRemnantArena/Outside/T_IconTipsInactive.T_IconTipsInactive/&gt;&lt;color=#fc6464&gt;Bộ bài của bạn phải chứa ít nhất 3 lá Vật phẩm Đặc biệt.&lt;/color&gt;</t>
         </is>
       </c>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Khi triển khai Echo này, sao chép một Novelty đã chọn trong Vùng Triển khai để triển khai. Lá sao chép sẽ bị tiêu hao vào cuối lượt (sao chép thất bại nếu Vùng Triển khai không còn ô trống).</t>
+          <t>Khi triển khai Echo này, sao chép một Novelty đã chọn trong Vùng Triển Khai để triển khai. Lá sao chép sẽ bị tiêu hao vào cuối lượt (sao chép thất bại nếu Vùng Triển Khai không còn ô trống).</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, hiển thị tối đa 3 Echoes có Rally từ bộ bài và thêm một trong số đó vào tay, sau đó xáo lại các lá không chọn vào bộ bài.</t>
+          <t>Khi triển khai Echo này, hiển thị tối đa 3 Echo có Tập Hợp từ bộ bài và thêm một trong số đó vào tay, sau đó xáo lại các lá không chọn vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, hiển thị tối đa 3 Echoes có Đồng Điệu từ bộ bài và thêm một trong số đó vào tay, sau đó xáo lại các lá không chọn vào bộ bài.</t>
+          <t>Khi triển khai Echo này, hiển thị tối đa 3 Echo có Đồng Điệu từ bộ bài và thêm một trong số đó vào tay, sau đó xáo lại các lá không chọn vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Hòa Âm&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Echo này ở trong Vùng Triển Khai (cả Hàng Trước lẫn Hàng Sau) cùng hai lá bài khác, tất cả sẽ nhận được {0} Sức Mạnh và Thể Chất khi kết thúc Giai Đoạn Triển Khai cho đến khi hiệp đấu kết thúc.&lt;/color&gt;</t>
+          <t>&lt;color=#e4c69b&gt;Hòa Âm&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Echo này ở trong Vùng Triển Khai (cả Hàng Trước lẫn Hàng Sau) cùng hai lá bài khác, tất cả sẽ nhận được {0} Sức Mạnh và Thể Chất khi kết thúc Giai Đoạn Triển Khai cho đến khi hiệp đấu kết thúc.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4050,10 +4050,10 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Phân tích mẫu sóng Rabelle cho thấy dạng dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả test nằm trong ngưỡng bình thường. 
-Kết luận: Mức Độ Tới Hạn Cộng Hưởng nằm trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Không có tiền sử cũng như nguy cơ hiện tại về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; vẫn ổn định.
+          <t>Phân tích mẫu sóng Rabelle cho thấy dạng dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả kiểm tra nằm trong ngưỡng bình thường. 
+Kết luận: Mức Độ Tới Hạn Cộng Hưởng nằm trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Không có tiền sử cũng như nguy cơ hiện tại về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; vẫn ổn định.
 Hiện tại không cần tư vấn tâm lý.
-&lt;i&gt;"Bài test diễn ra suôn sẻ. Lâu lắm rồi mới thấy một dạng sóng ổn định đến thế, gần như y hệt mẫu trong sách giáo khoa của thầy Rabelle… Thật sự, nó chuẩn đến mức hơi… bất thường."&lt;/i&gt;</t>
+&lt;i&gt;"Bài kiểm tra diễn ra suôn sẻ. Lâu lắm rồi mới thấy một dạng sóng ổn định đến thế, gần như y hệt mẫu trong sách giáo khoa của thầy Rabelle… Thật sự, nó chuẩn đến mức hơi… bất thường."&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Mornye, kỹ sư của Viện Nghiên Cứu Spacetrek Collective và giáo sư Khoa Kỹ thuật Exostrider tại Startorch Academy.
+          <t>Mornye, kỹ sư của Viện Nghiên cứu Spacetrek Collective và giáo sư Khoa Kỹ thuật Exostrider tại Học viện Startorch.
 Từng bước đi trên đôi chân giả đều đưa cô tiến gần hơn tới những vì sao trong giấc mơ.</t>
         </is>
       </c>
@@ -4189,11 +4189,11 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Phân tích dạng sóng của mẫu thử cho thấy mô hình dao động elip với miền thời gian ổn định. Mặc dù trước đây từng ghi nhận xu hướng dao động bất thường kéo dài, nhưng dạng sóng đã ổn định trở lại. Kết quả test nằm trong giới hạn bình thường. 
+          <t>Phân tích dạng sóng của mẫu thử cho thấy mô hình dao động elip với miền thời gian ổn định. Mặc dù trước đây từng ghi nhận xu hướng dao động bất thường kéo dài, nhưng dạng sóng đã ổn định trở lại. Kết quả kiểm tra nằm trong giới hạn bình thường. 
 Kết luận: Mức Cộng Hưởng Tới Hạn trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Hiện không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
 Resonator Mornye có tiền sử Quá Tải. Mức độ nghiêm trọng tối đa: Nhẹ. 
 Đối tượng từng tự kích hoạt một đợt Quá Tải ngắn cách đây vài năm để duy trì hoạt động của tháp tín hiệu quan trọng. Nhờ can thiệp y tế kịp thời, không xuất hiện triệu chứng hậu Quá Tải.
-Nên tiến hành test sức khỏe định kỳ. Tư vấn tâm lý hiện được đánh giá là không cần thiết.</t>
+Nên tiến hành kiểm tra sức khỏe định kỳ. Tư vấn tâm lý hiện được đánh giá là không cần thiết.</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sau khi vượt qua kỳ thi đầu vào, Lynae nhận được lá thư trúng tuyển chính thức, trở thành học viên của &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;. Ngày trước, một tờ giấy tương tự đã mở ra một hành trình vô định. Giờ đây, lá thư này đánh dấu cơ hội đầu tiên để cô tự chọn con đường và nơi mình thuộc về.</t>
+          <t>Sau khi vượt qua kỳ thi đầu vào, Lynae nhận được lá thư trúng tuyển chính thức, trở thành học viên của &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;. Ngày trước, một tờ giấy tương tự đã mở ra một hành trình vô định. Giờ đây, lá thư này đánh dấu cơ hội đầu tiên để cô tự chọn con đường và nơi mình thuộc về.</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Món quà từ một học trò mà Lynae từng giúp đỡ, tặng để chào mừng cô đến Học viện, được cho là thiết kế kinh điển trong bộ phim đường trường Liên bang New mà cô yêu thích.
+          <t>Món quà từ một học trò mà Lynae từng giúp đỡ, tặng để chào mừng cô đến Học viện, được cho là thiết kế kinh điển trong bộ phim đường trường Liên bang Mới mà cô yêu thích.
 Mềm mại, xanh mướt và có hình cây xương rồng, nhưng hoàn toàn không có gai, nằm không phải trên cát sỏi mà trên chiếc giường êm ái trong ký túc xá. Nó lặng lẽ canh giữ những giấc mơ đầy màu sắc sống động… nếu cậu có thể bỏ qua khuôn mặt biểu cảm độc đáo của nó.
 "Hả? Cái gối này á? Dễ thương quá! Và đây còn là phiên bản tái phát hành giới hạn nữa!"</t>
         </is>
@@ -4686,7 +4686,7 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>Mornye luôn trầm lặng, ít nhất đó là những gì bạn học cùng quê của cô từng nghĩ.
-Chiếc xe lăn cồng kềnh đã cô lập cô khỏi những trò chơi đuổi bắt vô tư của bạn bè từ khi còn nhỏ. Để bù đắp, cô dồn hết tâm sức phi thường vào việc học, lấp đầy từng khoảng trống thời gian bằng những trang sách và phép tính vô tận. Các thầy cô thường lấy cô làm tấm gương cho học sinh khác, cho đến khi chính họ cũng bắt đầu đuối sức theo kịp trí óc của cô. Giữa đám học sinh, lời đồn đoán lan truyền: cha cô làm việc cho một tập đoàn khét tiếng của Liên bang New, và mỗi ngày sau giờ học, một người hầu cứng nhắc sẽ xuất hiện, đẩy cô đi với sự chính xác lạnh lùng đến đáng sợ. Mornye ngồi trên xe như một con búp bê được sắp đặt cẩn thận, im lặng tuân theo.
+Chiếc xe lăn cồng kềnh đã cô lập cô khỏi những trò chơi đuổi bắt vô tư của bạn bè từ khi còn nhỏ. Để bù đắp, cô dồn hết tâm sức phi thường vào việc học, lấp đầy từng khoảng trống thời gian bằng những trang sách và phép tính vô tận. Các thầy cô thường lấy cô làm tấm gương cho học sinh khác, cho đến khi chính họ cũng bắt đầu đuối sức theo kịp trí óc của cô. Giữa đám học sinh, lời đồn đoán lan truyền: cha cô làm việc cho một tập đoàn khét tiếng của Liên bang Mới, và mỗi ngày sau giờ học, một người hầu cứng nhắc sẽ xuất hiện, đẩy cô đi với sự chính xác lạnh lùng đến đáng sợ. Mornye ngồi trên xe như một con búp bê được sắp đặt cẩn thận, im lặng tuân theo.
 Điều khiến bạn bè cô bất an hơn cả là sự từ chối thiện chí không ngừng của cô. Dù thầy cô đã dặn cả lớp phải quan tâm đến cô, dù các bạn khác đến gần với nụ cười thân thiện và hỏi han, cô vẫn cúi đầu, để mái tóc che mắt, lắc đầu nhẹ nhàng, từ chối tất cả trong im lặng.
 Lòng kiên nhẫn của trẻ con nào có dài lâu. Khi cái lợi thế của người ban ơn mất đi, sự xa lánh thầm lặng cũng lớn dần. Chẳng mấy chốc, khi cô lăn xe chầm chậm qua hành lang, chẳng ai lại gần. Họ trao nhau ánh mắt rồi lặng lẽ tránh ra, nhường cho chiếc xe một lối đi rộng thênh thang, như đàn cá chia dòng trước dòng nước.
 Mornye chưa bao giờ bận tâm đến những cử chỉ quan tâm lạnh nhạt ấy. Cô bám víu vào thành tích học tập, cách duy nhất để cô bày tỏ lòng biết ơn với thế giới trong im lặng, và cô biết nếu mình cầu cứu, dù vì cần thiết hay chỉ để chiều lòng, chắc chắn sẽ có người đáp lại.
@@ -4777,8 +4777,8 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ở &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;, không hề có sao trời.
-Hồi đó, Mảng Dự Báo Bầu Trời chỉ có thể tạo ra những kiểu mưa cơ bản nhất, còn &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; khi ấy vẫn còn trong giai đoạn thăm dò ban đầu, không có nguồn lực dư dả để tô điểm thế giới ngầm xa lạ bằng ánh sao.
+          <t xml:space="preserve">Ở &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;, không hề có sao trời.
+Hồi đó, Mảng Dự Báo Bầu Trời chỉ có thể tạo ra những kiểu mưa cơ bản nhất, còn &lt;te href=851071&gt;Tập Đoàn Spacetrek&lt;/te&gt; khi ấy vẫn còn trong giai đoạn thăm dò ban đầu, không có nguồn lực dư dả để tô điểm thế giới ngầm xa lạ bằng ánh sao.
 Nhưng Mornye không hề biết rằng những "ngôi sao" mà người thầy nhắc đến lại là những vì sao trên vùng đất băng giá.
 Chuyện xảy ra trong một chuyến thám hiểm đến vùng băng giá. Thông thường, chẳng ai nghĩ đến việc mời Mornye tham gia một nhiệm vụ như thế, nên khi người thầy đưa tay ra, cô không từ chối.
 Cô bước lên con tàu Starward Riseway hướng về thế giới bên trên. Ngạc nhiên thay, cô được đối xử không khác gì những người khác trong đội. Cô ngồi lặng lẽ trong chiếc xe rung rinh, phân tích dữ liệu thu thập được từ những cỗ máy gầm rú trong thời gian thực. Thỉnh thoảng, khi phương tiện không thể đi tiếp hoặc khi có điều gì đó đáng chú ý, người thầy lại cõng cô trên lưng, bước qua những lớp tuyết dày.
@@ -6971,7 +6971,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Domain là loại thẻ mới được thêm vào phiên bản Lahai-Roi của *Peaks of Prestige*. Những thẻ này sở hữu sức mạnh cực kỳ đáng gờm, có thể xoay chuyển cục diện của bất kỳ trận đấu nào.</t>
+          <t>Tổ Tacet là loại thẻ mới được thêm vào phiên bản Lahai-Roi của *Peaks of Prestige*. Những thẻ này sở hữu sức mạnh cực kỳ đáng gờm, có thể xoay chuyển cục diện của bất kỳ trận đấu nào.</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Mới Lạ là loại thẻ mới được bổ sung trong phiên bản Lahai-Roi của *Peaks of Prestige*. Chúng sở hữu những sức mạnh độc đáo. Khác với Echoes, Mới Lạ không trực tiếp tham gia Battle Stage, mà thay vào đó tác động lên chiến trường thông qua khả năng đặc biệt của mình.</t>
+          <t>Mới Lạ là loại thẻ mới được bổ sung trong phiên bản Lahai-Roi của *Peaks of Prestige*. Chúng sở hữu những sức mạnh độc đáo. Khác với Echo, Mới Lạ không trực tiếp tham gia Giai Đoạn Chiến Đấu, mà thay vào đó tác động lên chiến trường thông qua khả năng đặc biệt của mình.</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>Ashild lo lắng cho số phận của câu lạc bộ fan. Dù cô rất tin tưởng vào người đứng đầu, Anita, nhưng cho đến giờ, cô vẫn chưa thấy tia hy vọng nào từ các thành viên có thể đánh bại được mấy vị giáo sư.
-Đặc tính Đấu Thủ: None</t>
+Đặc tính Đấu Thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>Giáo sư Dennis cho rằng những trận đấu của các thành viên câu lạc bộ hâm mộ thiếu đi sự tao nhã và vẻ đẹp nghệ thuật cần thiết. Giờ đây, ông quyết tâm cải tổ tất cả theo lý tưởng của riêng mình.
-Đặc điểm Đấu Sĩ: None</t>
+Đặc điểm Đấu Sĩ: Không có</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>Giáo sư Festa tin rằng bà đã tìm ra thuật toán hoàn hảo cho các trận đấu—một thuật toán khiến bà bất bại trong mọi tình huống. Nhưng luôn có những biến số mà thuật toán không thể lường trước.
-Đặc tính đấu thủ: None</t>
+Đặc tính đấu thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       <c r="M109" t="inlineStr">
         <is>
           <t>Chessa chẳng mảy may quan tâm đến chuyện đấu tay đôi, cũng không bận tâm đến tương lai của câu lạc bộ fan. Với cô, phá hủy câu lạc bộ chỉ là một việc lặt vặt không thể tránh khỏi trong công việc nhàm chán hàng ngày.
-Duelist Traits: None</t>
+Đặc Tính Đấu Thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>Giáo sư Calith coi Furius, người sáng lập Peaks of Prestige, là kẻ thù không đội trời chung. Chiến dịch giải tán câu lạc bộ hâm mộ của ông có thể xuất phát từ mong muốn bảo vệ học trò khỏi bị cuốn theo... hoặc đơn giản chỉ là thù hằn cá nhân mà thôi.
-Đặc điểm Đấu Sĩ: None</t>
+Đặc điểm Đấu Sĩ: Không có</t>
         </is>
       </c>
     </row>
@@ -7827,8 +7827,8 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Anita, Quản lý Bộ phận của Lahai-Roi Ranked Tournament - Đỉnh Vinh Quang, thách đấu ngươi.
-Đặc điểm Duel thủ: None</t>
+          <t>Anita, Quản lý Bộ phận của Giải Đấu Xếp Hạng Lahai-Roi - Đỉnh Vinh Quang, thách đấu ngươi.
+Đặc điểm Đấu thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>Với Aya, Peaks of Prestige là cách để giải tỏa căng thẳng sau giờ học và là một phần không thể thiếu trong cuộc sống của cô.
-Đặc điểm Duelist: None</t>
+Đặc điểm Duelist: Không có</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       <c r="M113" t="inlineStr">
         <is>
           <t>Các y tá cơ khí có dùng combo điện không? Đừng bỏ lỡ trên kênh *Peaks of Prestige* nhé!
-Đặc tính Đấu Thủ: None</t>
+Đặc tính Đấu Thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       <c r="M114" t="inlineStr">
         <is>
           <t>Có vẻ I.R.I.S. đã chuyển sang một nhân cách kỳ lạ nhưng quen thuộc. Hơi lo ngại thật… nhưng trước hết, hãy đấu một trận đã.
-Đặc điểm Duel thủ: None</t>
+Đặc điểm Đấu thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>Khi Zahira mang *Peaks of Prestige* từ Học viện về bộ tộc Roya, cô chưa từng nghĩ rằng nó sẽ lan nhanh khắp rừng Bjartr như ngọn lửa hoang dã.
-Đặc tính đấu sĩ: None</t>
+Đặc tính đấu sĩ: Không có</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>Lagerith theo đuổi sức mạnh để bảo vệ điều quý giá với cô. Giờ đây, Peaks of Prestige dường như đã trở thành một trong những nguồn sức mạnh của cô.
-Đặc tính Đấu Sĩ: None</t>
+Đặc tính Đấu Sĩ: Không có</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>Katrina muốn rời Lahai-Roi để trở thành một Võ sĩ Septimont... Có lẽ một ngày nào đó, giấc mơ của cô sẽ thành hiện thực.
-Đặc tính Võ sĩ: None</t>
+Đặc tính Võ sĩ: Không có</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Challenge Jonna à! Cho cô ta thấy ai mới là Duelist thực thụ!
+          <t>Thử Thách Jonna à! Cho cô ta thấy ai mới là Duelist thực thụ!
 Đặc Tính Duelist: Mỗi khi Duelist triển khai Echo, Echo đó sẽ nhận được Kháng Cự.</t>
         </is>
       </c>
@@ -8436,8 +8436,8 @@
           <t>Suốt mấy ngày qua, chúng tôi theo dấu một "bầy tuần lộc cơ khí" băng qua vùng băng giá. Hành trình đưa chúng tôi qua những hẻm núi với vách đá hình khối và hàng loạt tượng đài đứng sừng sững, cuối cùng dẫn đến việc phát hiện một "thiên đường ngầm" rộng lớn dưới lớp băng vĩnh cửu. Tại đó, chúng tôi gặp một bộ tộc cổ xưa của loài người: Roya.
 Về mặt sinh lý, Roya không khác chúng ta là mấy. Điểm khác biệt chủ yếu nằm ở những đặc điểm tinh tế mà họ phát triển để sống sót trong cái lạnh khắc nghiệt. Trong hang động ngầm khổng lồ này, một nguồn năng lượng kỳ diệu mà người Roya gọi là "Trái Tim Baldur" đang không ngừng tỏa sáng, cung cấp ánh sáng và hơi ấm cần thiết để duy trì sự sống dưới lòng đất. Dưới "ánh mặt trời" ấy, người Roya đã xây dựng một mái ấm mới. Qua vô số thế hệ, họ nghiên cứu nhịp điệu của Trái Tim Baldur, tạo ra hệ thống tính thời gian riêng để đánh dấu chu kỳ ngày đêm, mùa màng và năm tháng, sống hòa quyện với thế giới bên trên trong tĩnh lặng.
 Theo thần thoại của Roya, những "sinh vật cơ khí" lang thang trên vùng băng giá—mà họ gọi là Soliskin, còn chúng ta phân loại là Exoswarm—là những tia lửa trong ý thức của chính Baldur. Để tỏ lòng biết ơn ánh sáng mà Baldur ban tặng, người Roya đã gánh vác một sứ mệnh thiêng liêng qua các thế hệ: dẫn dắt những Soliskin lạc lối trở về nơi trú ẩn này và chung sống cùng chúng. Sau hàng thiên niên kỷ tắm trong ánh sáng của Reactor Drive, người Roya ngày nay có thể đi lại trên vùng băng giá chỉ với vài lớp áo mỏng của Lahai-Roi.
-Chúng ta từng ca ngợi Lahai-Roi là một trong những phát hiện khoa học vĩ đại nhất thế kỷ, nhưng lại không công bố rộng rãi. Ban lãnh đạo Pioneer Association đồng ý rằng việc tiết lộ "sự thật chấn động" này có thể gây ra những hậu quả khó lường. Người Roya, sống biệt lập qua nhiều thế hệ, có thể sẽ nảy sinh sự tò mò sâu sắc về thế giới bên ngoài, trong khi nền văn minh hiện đại cũng sẽ đưa ra những phán xét của riêng mình về nền văn minh cổ xưa này.
-Liệu điều này sẽ dẫn đến sự giao lưu và chung sống, hay xâm phạm và lợi dụng? Không ai có thể đảm bảo kết quả. Vì vậy, Pioneer Association phải xử lý báo cáo nghiên cứu này với sự thận trọng tối đa.</t>
+Chúng ta từng ca ngợi Lahai-Roi là một trong những phát hiện khoa học vĩ đại nhất thế kỷ, nhưng lại không công bố rộng rãi. Ban lãnh đạo Hiệp hội Pioneer đồng ý rằng việc tiết lộ "sự thật chấn động" này có thể gây ra những hậu quả khó lường. Người Roya, sống biệt lập qua nhiều thế hệ, có thể sẽ nảy sinh sự tò mò sâu sắc về thế giới bên ngoài, trong khi nền văn minh hiện đại cũng sẽ đưa ra những phán xét của riêng mình về nền văn minh cổ xưa này.
+Liệu điều này sẽ dẫn đến sự giao lưu và chung sống, hay xâm phạm và lợi dụng? Không ai có thể đảm bảo kết quả. Vì vậy, Hiệp hội Pioneer phải xử lý báo cáo nghiên cứu này với sự thận trọng tối đa.</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
 Đối với Roya, việc phơi bày bản thân trước thế giới bên ngoài có thể là một canh bạc. Nhưng họ tin rằng một khi Threnodian xa lạ này thức tỉnh, quy mô hủy diệt của nó sẽ nhấn chìm toàn bộ Solaris... Và vì điều đó, họ đã chuẩn bị tinh thần.
 Vì thế, mỗi quốc gia đều tuyên bố lập trường của mình: Liên Minh Cực Địa sẽ chính thức thiết lập liên minh với Roya và tiến hành các cuộc thám hiểm chung vào Lahai-Roi. Đồng thời, mọi hoạt động của Liên Minh đều phải dựa trên nền tảng các thỏa thuận hòa bình, không gây tổn hại hay xáo trộn đến xã hội Roya.
 Hội nghị kết thúc trong hòa khí, nhưng chẳng ai ra về với tâm trạng nhẹ nhõm. Chúng ta đến đây vì tò mò về những bí ẩn của Lahai-Roi, để rồi ra đi chỉ với nỗi sợ hãi trước chính những điều chưa biết ấy.
-Như lời của vị học giả cuối cùng thuộc New Federation trước khi rời đi: "Nỗi sợ này... khó mà gọi tên, nhưng đó là nỗi sợ cổ xưa và mạnh mẽ nhất trong chúng ta. Và với nhân loại, nỗi sợ ấy luôn là nỗi sợ trước những điều chưa biết."</t>
+Như lời của vị học giả cuối cùng thuộc Liên Bang Mới trước khi rời đi: "Nỗi sợ này... khó mà gọi tên, nhưng đó là nỗi sợ cổ xưa và mạnh mẽ nhất trong chúng ta. Và với nhân loại, nỗi sợ ấy luôn là nỗi sợ trước những điều chưa biết."</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
 “Hãy tiếp tục sống,”
 Người phán vậy.
 —Trích đoạn từ bài dân ca Royan &lt;i&gt;Vì Người Khổng Lồ Đã Ở Đây&lt;/i&gt;
-Theo thần thoại Royan và những ghi chép lịch sử còn sót lại, trước khi Lament giáng xuống Lahai-Roi, người Roya từng sống trên mặt đất, giữa những cánh rừng vịnh hẹp. Nhưng sau Lament, ▇▇▇▇▇▇ của Solaris trải qua những biến đổi khủng khiếp. Nhiệt độ giảm mạnh, tiếp đó là sự sụp đổ của ▇▇▇▇ và ▇▇▇.
+Theo thần thoại Royan và những ghi chép lịch sử còn sót lại, trước khi Lời Than Vãn giáng xuống Lahai-Roi, người Roya từng sống trên mặt đất, giữa những cánh rừng vịnh hẹp. Nhưng sau Lời Than Vãn, ▇▇▇▇▇▇ của Solaris trải qua những biến đổi khủng khiếp. Nhiệt độ giảm mạnh, tiếp đó là sự sụp đổ của ▇▇▇▇ và ▇▇▇.
 Người Roya thời đó chỉ còn biết trú ẩn trong đống đổ nát của ▇▇▇▇, lang thang trên vùng băng giá hoang tàn, tìm kiếm sự sống trên những đồng bằng phủ đầy tuyết mới.</t>
         </is>
       </c>
@@ -8874,16 +8874,16 @@
 Năng lượng từ Reactor Drive chảy qua ███, liên tục nuôi dưỡng và duy trì thứ gì đó bên trong ██. Điều này dường như duy trì một hệ thống kín.
 [00:06:22]
 Tethys xác nhận tần số ██ yếu ớt bắt nguồn từ bên ngoài ██.
-Viện Nghiên Cứu đã đưa ra một số giả thuyết. Giả thuyết phổ biến nhất cho rằng:
+Viện Nghiên cứu đã đưa ra một số giả thuyết. Giả thuyết phổ biến nhất cho rằng:
 Dưới ▇▇ là một ▇▇ kết nối ▇▇▇▇. ▇▇ tồn tại để cắt đứt mối liên hệ đó.
-▇▇ chỉ bịt kín một phần của ██; phần còn lại phân tán về phía Lahai-Roi, tồn tại dưới dạng Void Storm và ▇▇▇.
+▇▇ chỉ bịt kín một phần của ██; phần còn lại phân tán về phía Lahai-Roi, tồn tại dưới dạng Bão Hư Không và ▇▇▇.
 [00:07:01]
 Nếu ▇▇ bị hư hại, hai nguồn ██ vốn bị tách rời sẽ hợp nhất trở lại, khôi phục hình dạng hoàn chỉnh. Điều đó sẽ là… ▇▇ của Solaris.
 [00:08:33]
 Các ghi chép khác của Royan nhắc đến con đường mà Exostrider từng đi qua nằm ngoài ▇▇. "Con đường" này có thể là một ▇▇ thực sự, kết nối trực tiếp với ▇▇▇▇.
 [00:09:10]
 Điều gì nằm ngoài cánh cổng đó?
-▇▇▇? Vũ trụ? Etheric Seaic đã chặn đường lên trên.
+▇▇▇? Vũ trụ? Biển Etheric đã chặn đường lên trên.
 Con đường xuống dưới có thể là lối đi duy nhất còn lại.
 [00:09:45]
 Như trên, cũng như dưới...
@@ -8893,7 +8893,7 @@
 [00:10:00]
 Chú ý: Dự án "Sundermere Lakebed - Aleph-1" hiện được phân loại là khu vực cấm.
 Mọi hành động tiếp cận ▇▇ sẽ bị coi là can thiệp trực tiếp vào ▇▇.
-Warning: bản ghi này sẽ tự chấm dứt sau âm thanh "▇▇▇".
+Cảnh báo: bản ghi này sẽ tự chấm dứt sau âm thanh "▇▇▇".
 [00:10:78]
 …như ▇… ▇▇… như ▇… dưới… ▇…
 [00:10:66]
@@ -8979,14 +8979,14 @@
           <t>Sau nhiều vòng đàm phán, Roya và Liên Minh Cực Địa đã đạt được thỏa thuận chung xây dựng các cơ sở khoa học quanh ba địa điểm trọng yếu: thanh đại kiếm của Exostrider trên vùng băng giá, Sundermere trong hang động ngầm, và Etching Plains.
 Solisylum cung cấp dữ liệu quan trọng về chu kỳ vận hành của Reactor Drive và các chỉ số vùng Void Storm, giúp lên kế hoạch hạ tầng quy mô lớn. Đồng thời, các Shepherd của Roya điều phối Exoswarm trong công tác khai quật, vận chuyển và hậu cần, đảm bảo dự án tiến triển liên tục.
 Qua sự hợp tác này, Liên Minh Cực Địa hoàn thành giai đoạn đầu mở rộng: Trạm Nghiên cứu Cực Địa Frostlands, tiếp đó là Starward Riseway – thang máy vận tải thẳng đứng khổng lồ được xây dựng trực tiếp trên thanh đại kiếm của Exostrider.
-Cùng thời điểm, New Federation đóng góp công nghệ kỹ thuật không gian tiên tiến nhất để xây dựng Viện Nghiên Cứu Spacetrek. Cơ sở hình vòng này hoạt động trong dải trọng lực thấp cục bộ, duy trì quỹ đạo ổn định để liên tục quét và thăm dò sâu vào thanh đại kiếm do Exostrider để lại.
+Cùng thời điểm, Liên Bang Mới đóng góp công nghệ kỹ thuật không gian tiên tiến nhất để xây dựng Viện Nghiên cứu Spacetrek. Cơ sở hình vòng này hoạt động trong dải trọng lực thấp cục bộ, duy trì quỹ đạo ổn định để liên tục quét và thăm dò sâu vào thanh đại kiếm do Exostrider để lại.
 Dựa trên phân tích không xâm lấn sâu rộng về Exostrider và Exoswarm, kết hợp với dữ liệu do Roya cung cấp, Liên Minh Cực Địa đã đưa ra những kết luận sau:
 1. Về Mối Quan Hệ Giữa Exostrider và Sentinel
 Exostrider thể hiện mức độ tương đồng sinh học cực cao với Sentinel, song cấu hình chức năng lại hoàn toàn khác biệt. Nó không sở hữu năng lực nhận thức tiên tri và dẫn dắt văn minh như Sentinel.
 Thay vào đó, thế mạnh của nó nằm ở khả năng chiến đấu chuyên biệt, tính cơ động vượt trội và khả năng thích ứng sinh cơ học nổi bật. Từ những đặc điểm này, các nhà nghiên cứu đưa ra giả thuyết rằng Exostrider là một ███ trong hệ thống ███, đảm nhiệm vai trò vận tải và chiến tranh. Để phân biệt, Viện chính thức định danh Exostrider là "Bản Sao Sentinel".
-2. Về Bản Chất Physical của Exostrider
+2. Về Bản Chất Vật Lý của Exostrider
 Dưới tác động và xúc tác của Reactor Drive, các bộ phận tách rời từ cơ thể Exostrider phân hóa thành hai loại thực thể Exoswarm: dạng động vật và dạng thực vật. Những sinh vật độc đáo này thay thế hệ động thực vật đã tuyệt chủng của Lahai-Roi, ổn định và hỗ trợ hệ sinh thái mong manh của nó. Khi được cung cấp đủ năng lượng hoặc sạc đầy, Exoswarm sẽ quay trở lại Exostrider và hợp nhất lại vào khung xương của nó, sửa chữa các phần bị hư hại.
-Tuy nhiên, các ghi chép dài hạn của Roya về quá trình phân hóa và chu kỳ thế hệ của Exoswarm cho thấy quá trình phục hồi sinh cơ học này là có giới hạn. Like tế bào người, Exoswarm có số lần phân chia tối đa. Theo thời gian, khoảng thời gian tái sinh kéo dài, tỷ lệ phân hóa mới giảm dần, và cuối cùng quá trình này sẽ dừng hẳn.
+Tuy nhiên, các ghi chép dài hạn của Roya về quá trình phân hóa và chu kỳ thế hệ của Exoswarm cho thấy quá trình phục hồi sinh cơ học này là có giới hạn. Giống như tế bào người, Exoswarm có số lần phân chia tối đa. Theo thời gian, khoảng thời gian tái sinh kéo dài, tỷ lệ phân hóa mới giảm dần, và cuối cùng quá trình này sẽ dừng hẳn.
 Dự báo của chúng tôi còn đáng lo ngại hơn. Tính toán cho thấy tổng số đơn vị Exoswarm đã được tái hấp thụ, cộng với sản lượng tiềm năng tối đa từ quá trình phân hóa trong tương lai, vẫn không đủ để khôi phục hoàn toàn cấu trúc của Exostrider. Điều này cho thấy sự suy giảm nghiêm trọng và dài hạn của quần thể Exoswarm. Trong khi một phần tổn thất này là do sự săn mồi của Voidworm, một lượng lớn các bộ phận bị mất tích vẫn chưa được giải thích.</t>
         </is>
       </c>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Report Bổ sung: Đặc tính Hoạt động của Exostrider và Lò Phản ứng
+          <t>Báo cáo Bổ sung: Đặc tính Hoạt động của Exostrider và Lò Phản ứng
 Các cuộc điều tra và chẩn đoán mức năng lượng tiếp theo tại nơi trú ẩn ngầm Lahai-Roi xác nhận rằng, ngay cả khi ở trạng thái ngủ đông, Exostrider vẫn tiếp tục thực hiện bản năng tự điều chỉnh để bảo vệ cả khu vực và Roya.
 Dữ liệu khảo sát cho thấy không phải tất cả các bộ phận tách rời khỏi Exostrider đều biến đổi thành các đơn vị Exoswarm có tri giác. Một phần đáng kể thay vào đó chuyển hóa thành các cấu trúc sinh học tích hợp trong các tầng địa chất. Những cấu trúc này phân nhánh và liên kết như đốt sống, hiện được phân loại là Gai Dưới Vỏ. Phân bố đồng đều trên các vùng kiến tạo không ổn định, chúng được cho là đóng vai trò quan trọng trong việc duy trì tính toàn vẹn của vỏ Trái Đất và dẫn truyền năng lượng từ Lò Phản ứng.
 Về Mối Quan hệ Giữa Lò Phản ứng và Thân thể Exostrider:
@@ -9174,46 +9174,46 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Cẩm Nang Sinh Viên Học Viện Startorch: Guide Định Hướng (Trích Đoạn)
+          <t>Cẩm Nang Sinh Viên Học Viện Startorch: Hướng Dẫn Định Hướng (Trích Đoạn)
 Tuyên Ngôn Sinh Viên Học Viện Startorch
 Dưới ánh sao Startorch, chúng ta nguyện mang ngọn lửa của nó tiến về phía trước, sát cánh cùng những tâm hồn đồng điệu, và đẩy lùi ranh giới của tri thức. Mỗi cuộc truy tìm chân lý sẽ là một tia sáng chống lại màn đêm dài đằng đẵng cho đến khi nó tàn lụi. Cùng nhau, chúng ta xây dựng một bình minh thuộc về chính mình.
 I. Chương Trình Học
 Học Viện Startorch áp dụng mô hình "2 Năm Dự Bị + 4 Năm Chuyên Ngành".
 a. Chương Trình Dự Bị (Năm 1–2)
-Tất cả sinh viên (trừ các Synchronist được nhận vào Rabelle College) đều bắt đầu với chương trình học liên ngành. Các em sẽ được trang bị kiến thức cơ bản về khoa học tự nhiên, khoa học nhân văn, và các kỹ năng sinh tồn thiết yếu để sống tại Lahai-Roi. Việc phân bổ vào khoa chuyên ngành sẽ được quyết định vào cuối Năm 2, dựa trên nguyện vọng và thành tích học tập của các em.
-Lưu Ý Special: Các Synchronist thuộc Rabelle College sẽ được xếp vào khoa ngay khi nhập học, theo một lộ trình đào tạo riêng biệt và được miễn các môn dự bị chung.
+Tất cả sinh viên (trừ các Đồng Bộ Giả được nhận vào Rabelle College) đều bắt đầu với chương trình học liên ngành. Các em sẽ được trang bị kiến thức cơ bản về khoa học tự nhiên, khoa học nhân văn, và các kỹ năng sinh tồn thiết yếu để sống tại Lahai-Roi. Việc phân bổ vào khoa chuyên ngành sẽ được quyết định vào cuối Năm 2, dựa trên nguyện vọng và thành tích học tập của các em.
+Lưu Ý Đặc Biệt: Các Đồng Bộ Giả thuộc Rabelle College sẽ được xếp vào khoa ngay khi nhập học, theo một lộ trình đào tạo riêng biệt và được miễn các môn dự bị chung.
 b. Chương Trình Chuyên Ngành (Năm 3–6)
 Giai đoạn này tập trung đào tạo các chuyên gia nghiên cứu. Các em sẽ được khuyến khích tham gia các nhóm nghiên cứu và thấm nhuần tinh thần "học thông qua nghiên cứu". Những sinh viên xuất sắc có định hướng gắn bó lâu dài với Học Viện sẽ nhận được sự hỗ trợ từ phía tổ chức.
 II. Các Khoa Chuyên Ngành
 Học Viện Startorch được tổ chức xoay quanh việc nghiên cứu Exostrider và hệ sinh thái độc đáo của Lahai-Roi. Bốn khoa chuyên ngành bao gồm:
 a. Rabelle College (Bộ Môn Đào Tạo Đồng Bộ / Bộ Môn Nghiên Cứu Cổ Sinh)
-Chuyên về tuyển chọn và đào tạo Resonators Tăng Cường – những cá nhân có khả năng đồng bộ ngoài cơ thể với Exostrider.
-Được đặt theo tên của Scott Rabelle, người phát minh ra Rabelle's Curve, khoa này áp dụng các phương pháp định lượng nghiêm ngặt để đào tạo ra những Synchronist đủ tiêu chuẩn. Thường được gọi là "Khoa Đồng Bộ", nó đóng vai trò trung tâm của Học Viện, cung cấp nền tảng công nghệ cho nhiều lĩnh vực khác.
-Khoa được trang bị buồng mô phỏng cơ-neural được chế tạo từ các bộ phận của Exostrider, có khả năng tái tạo tải trọng đồng bộ trong quá trình điều khiển. Công nghệ giám sát an toàn được phát triển tại đây đã được Đơn Vị Điều Dưỡng Resonators chuyển hóa thành môn "Trị Liệu Tần Số", mang lại lợi ích cho toàn thể cộng đồng trong Academy.
+Chuyên về tuyển chọn và đào tạo Resonator Tăng Cường – những cá nhân có khả năng đồng bộ ngoài cơ thể với Exostrider.
+Được đặt theo tên của Scott Rabelle, người phát minh ra Đường Cong Rabelle, khoa này áp dụng các phương pháp định lượng nghiêm ngặt để đào tạo ra những Đồng Bộ Giả đủ tiêu chuẩn. Thường được gọi là "Khoa Đồng Bộ", nó đóng vai trò trung tâm của Học Viện, cung cấp nền tảng công nghệ cho nhiều lĩnh vực khác.
+Khoa được trang bị buồng mô phỏng cơ-neural được chế tạo từ các bộ phận của Exostrider, có khả năng tái tạo tải trọng đồng bộ trong quá trình điều khiển. Công nghệ giám sát an toàn được phát triển tại đây đã được Đơn Vị Điều Dưỡng Resonator chuyển hóa thành môn "Trị Liệu Tần Số", mang lại lợi ích cho toàn thể cộng đồng trong Học Viện.
 b. Khoa Kỹ Thuật Exostrider (Bộ Môn Đồng Bộ Người-Máy / Bộ Môn Phát Triển Chiến Thuật)
 Chuyên về tích hợp cơ khí và nghiên cứu trang thiết bị chiến thuật.
 Nhờ khai thác đặc tính tự nhân bản của các bộ phận Exostrider, khoa này phát triển các loại máy móc thông minh, vũ khí module hóa, và tiến hành thử nghiệm ứng dụng trong môi trường chiến đấu mô phỏng. Khoa còn đảm nhiệm sứ mệnh quan trọng là đẩy nhanh quá trình phục hồi Exostrider thông qua việc thu thập và nuôi cấy các bộ phận bên ngoài.
 c. Khoa Vật Chất Hư Không (Bộ Môn Bóp Méo Không Gian)
 Chuyên nghiên cứu về các dị thường không gian và vật lý Vật Chất Hư Không.
-Nghiên cứu về Exostrider của khoa đã tạo ra các công nghệ truyền thông và neo giữ không gian, cho phép theo dõi xuyên chiều và giám sát dấu hiệu sinh tồn của Synchronist.
-Chủ đề nghiên cứu cốt lõi của khoa xoay quanh việc giải mã nguồn gốc của Hiện Tượng Waveworn. Bằng cách quan sát các Cơn Void Storm khu vực và phân tích các sự kiện tương tự trên toàn cầu, khoa hướng tới xây dựng một hệ thống cảnh báo sớm thảm họa đáng tin cậy. Vì lý do này, khoa hợp tác chặt chẽ với Black Shores.
-d. Khoa Khoa Học Năng Lượng Light (Bộ Môn Kỹ Thuật Mảng Light / Bộ Môn Bảo Tồn Sinh Thái)
+Nghiên cứu về Exostrider của khoa đã tạo ra các công nghệ truyền thông và neo giữ không gian, cho phép theo dõi xuyên chiều và giám sát dấu hiệu sinh tồn của Đồng Bộ Giả.
+Chủ đề nghiên cứu cốt lõi của khoa xoay quanh việc giải mã nguồn gốc của Hiện Tượng Waveworn. Bằng cách quan sát các Cơn Bão Hư Không khu vực và phân tích các sự kiện tương tự trên toàn cầu, khoa hướng tới xây dựng một hệ thống cảnh báo sớm thảm họa đáng tin cậy. Vì lý do này, khoa hợp tác chặt chẽ với Black Shores.
+d. Khoa Khoa Học Năng Lượng Ánh Sáng (Bộ Môn Kỹ Thuật Mảng Ánh Sáng / Bộ Môn Bảo Tồn Sinh Thái)
 Chuyên về chuyển đổi năng lượng quang tử và duy trì hệ sinh thái.
-Bộ Môn Kỹ Thuật Mảng Light nghiên cứu cơ chế chuyển hóa và lưu trữ năng lượng từ Mảng Thấu Kính Solis của Solisylum, tạo ra nguồn ánh sáng cho Lò Phản Ứng cung cấp năng lượng cho hoạt động của Academy.
+Bộ Môn Kỹ Thuật Mảng Ánh Sáng nghiên cứu cơ chế chuyển hóa và lưu trữ năng lượng từ Mảng Thấu Kính Solis của Solisylum, tạo ra nguồn ánh sáng cho Lò Phản Ứng cung cấp năng lượng cho hoạt động của Học Viện.
 Bộ Môn Sinh Thái, đặt tại Exo Genesis Labs và gắn bó chặt chẽ với công tác bảo tồn âm sinh thái, được gọi không chính thức là "Cánh Nông Học". Thông qua nghiên cứu hành vi của các đơn vị Exoswarm, các nhà khoa học hướng tới hiểu biết về nhận thức của Exostrider và vai trò của nó trong việc định hình lại Hệ Âm Sinh của Lahai-Roi.
 III. Tổng Quan Về Các Môn Học
-Yêu Cầu General
-a. Lịch Sử Lahai-Roi: Khám phá câu chuyện của vùng đất này và nguồn gốc của Academy.
-b. Văn hóa Roya: Tìm hiểu về truyền thống và xã hội bản địa. (Sinh viên Roya có thể miễn môn này và làm trợ giảng để lấy điểm cộng.)
+Yêu Cầu Chung
+a. Lịch Sử Lahai-Roi: Khám phá câu chuyện của vùng đất này và nguồn gốc của Học Viện.
+b. Văn Hóa Roya: Tìm hiểu về truyền thống và xã hội bản địa. (Sinh viên Roya có thể miễn môn này và làm trợ giảng để lấy điểm cộng.)
 c. Quy Trình Phòng Thí Nghiệm: Nền tảng của thực hành nghiên cứu và an toàn phòng thí nghiệm.
 d. Nghiên Cứu Bảo Mật: Nắm vững các quy định an ninh cần thiết để hoàn thành chương trình sáu năm.
 Môn Tự Chọn Nổi Bật
 a. Đào Tạo Vận Hành Phương Tiện: Làm chủ các kỹ năng di chuyển thiết yếu tại Lahai-Roi.
 b. Rèn Luyện Thể Chất: Xây dựng một thể chất đủ sức theo kịp một tinh thần khắc nghiệt. (Bắt buộc đối với tất cả sinh viên Rabelle College.)
 Giới Thiệu Các Môn Chuyên Ngành
-Các môn học của từng khoa được sắp xếp theo khối giảng dạy để tối ưu hóa hiệu quả. Các Synchronist của Rabelle College có thể đăng ký học xuyên khoa, giúp họ trở thành những học giả đa năng, xuất sắc hàng đầu. Những ai hoàn thành lộ trình này sẽ được coi là biểu tượng của sự kiên trì và trí tuệ.
+Các môn học của từng khoa được sắp xếp theo khối giảng dạy để tối ưu hóa hiệu quả. Các Đồng Bộ Giả của Rabelle College có thể đăng ký học xuyên khoa, giúp họ trở thành những học giả đa năng, xuất sắc hàng đầu. Những ai hoàn thành lộ trình này sẽ được coi là biểu tượng của sự kiên trì và trí tuệ.
 Hãy để bình minh làm chứng, và ý chí của chúng ta là ngọn đuốc. Mỗi buổi điểm danh lúc 8 giờ sáng là một lời tái khẳng định cam kết với con đường khoa học.
-(Tài liệu này có thể được cập nhật. Vui lòng luôn tham khảo các thông báo chính thức mới nhất từ Academy.)</t>
+(Tài liệu này có thể được cập nhật. Vui lòng luôn tham khảo các thông báo chính thức mới nhất từ Học Viện.)</t>
         </is>
       </c>
     </row>
@@ -9296,11 +9296,11 @@
 "Chúng tôi đã gặp phải một hiện tượng bất ngờ trên vùng băng giá. Tuyết lở, hố sụt đột ngột, những vết nứt lấp lánh ánh địa quang kỳ lạ và dữ dội… và trên luồng sáng đó, chúng tôi thấy một màn sương ảo giác lơ lửng trong không trung. Chẳng bao lâu sau, chúng tôi bị tấn công trực diện bởi thứ mà tôi chỉ có thể gọi là 'Cơn Bão Vô Hình.'"
 "Một… một tiếng gầm thét vang lên từ hướng luồng sáng. Cơn bão ấy… cuốn lấy chúng tôi. Chúng tôi cố rút lui vào hang động này. Đây là nơi duy nhất an toàn. Nhưng…"
 "Hiện tại, tất cả thành viên trong đoàn thám hiểm… ngoại trừ tôi… đều đã chết. Hay… chính xác hơn… họ đều đã 'biến mất.'"
-"Tôi đã tập hợp tất cả Terminal của họ tại nơi trú ẩn này. Đó là nguyện vọng cuối cùng của họ. Dữ liệu trên đó về hiện tượng này rất quan trọng. Phải được thu hồi."
-"Còn bản thân tôi… hậu quả của 'thảm họa' đó đã khiến tôi không thể di chuyển. Tôi không còn đủ sức để quay về Viện. Vậy nên… trong khoảng thời gian còn lại, tôi sẽ dùng Terminal tại hiện trường để ghi lại mọi thay đổi trong cơ thể và tần số của mình. Hy vọng nó sẽ là manh mối cho những người đến sau về thứ mà chúng ta đang phải đối mặt…"
-"Xin hãy… để Terminal này tồn tại lâu hơn tôi."
+"Tôi đã tập hợp tất cả Thiết bị đầu cuối của họ tại nơi trú ẩn này. Đó là nguyện vọng cuối cùng của họ. Dữ liệu trên đó về hiện tượng này rất quan trọng. Phải được thu hồi."
+"Còn bản thân tôi… hậu quả của 'thảm họa' đó đã khiến tôi không thể di chuyển. Tôi không còn đủ sức để quay về Viện. Vậy nên… trong khoảng thời gian còn lại, tôi sẽ dùng Thiết bị đầu cuối tại hiện trường để ghi lại mọi thay đổi trong cơ thể và tần số của mình. Hy vọng nó sẽ là manh mối cho những người đến sau về thứ mà chúng ta đang phải đối mặt…"
+"Xin hãy… để Thiết bị đầu cuối này tồn tại lâu hơn tôi."
 "Chức năng cơ thể… vẫn bình thường. Nhưng… tôi cảm thấy cơ thể mình đang nhẹ dần. Như thể đang trôi nổi…"
-"Terminal dường như bị %...&amp;* hỏng… Nhiễu %...&amp; ngày càng tăng…"
+"Thiết bị đầu cuối dường như bị %...&amp;* hỏng… Nhiễu %...&amp; ngày càng tăng…"
 "...Cơ thể tôi… có vẻ %...&amp; đang trở nên trong suốt…"
 "￥%...&amp;khô&amp;*ng th…ể chạm… vào #￥%... bất cứ thứ gì…"
 "...&amp;*khô&amp;*ng th…ể nhìn thấy gì %... &amp;nữa… #￥%*..."
@@ -9383,11 +9383,11 @@
         <is>
           <t>Thưa đồng bào, hôm nay chúng ta tụ họp dưới Reactor Drive không chỉ để kỷ niệm một cột mốc trong lịch sử thám hiểm Lahai-Roi, mà còn để tưởng nhớ... Toàn bộ đội thám hiểm khoa học Roald đã hy sinh trên vùng đất băng giá này.
 Thay mặt tất cả thành viên của Spacetrek Collective, tôi xin gửi lời tri ân sâu sắc nhất và tưởng nhớ đến Đại úy Roald cùng mọi thành viên trong đội của ông.
-Qua dữ liệu chi tiết và những bản ghi cuối cùng được lưu giữ trong Terminal của Đại úy Roald và các thành viên trong đội, cuối cùng chúng ta đã làm sáng tỏ bản chất của "cơn bão vô hình" quét qua vùng băng giá. Dựa trên đặc tính và tác động của nó, chúng tôi chính thức đặt tên cho hiện tượng này—Void Storm.
-Void Storm là một thảm họa thứ cấp được kích hoạt bởi Threnodian có tên Aleph-1. Sự xuất hiện của nó thường được báo trước bởi những luồng địa quang dữ dội, và chính vì lý do đó mà hiện tượng khí tượng bất thường mang tên "Shimmer" đã trở thành lời cảnh báo đầu tiên của chúng ta. Nơi nào Shimmer tụ lại, Void Storm sẽ sớm kéo đến.
+Qua dữ liệu chi tiết và những bản ghi cuối cùng được lưu giữ trong Thiết bị đầu cuối của Đại úy Roald và các thành viên trong đội, cuối cùng chúng ta đã làm sáng tỏ bản chất của "cơn bão vô hình" quét qua vùng băng giá. Dựa trên đặc tính và tác động của nó, chúng tôi chính thức đặt tên cho hiện tượng này—Bão Hư Không.
+Bão Hư Không là một thảm họa thứ cấp được kích hoạt bởi Threnodian có tên Aleph-1. Sự xuất hiện của nó thường được báo trước bởi những luồng địa quang dữ dội, và chính vì lý do đó mà hiện tượng khí tượng bất thường mang tên "Shimmer" đã trở thành lời cảnh báo đầu tiên của chúng ta. Nơi nào Shimmer tụ lại, Bão Hư Không sẽ sớm kéo đến.
 Bất kỳ sinh vật sống nào bị cuốn vào đều chịu tác động chết người, mất đi mọi sinh khí. Đây không phải cái chết sinh học, mà là sự tan rã của chính tần số. Hình hài tan vỡ. Thân thể trở nên trong suốt, rồi lặng im, cho đến khi hòa tan vào hư vô. Những ai sống sót sau lần tiếp xúc đầu tiên sẽ thấy tần số của mình chập chờn như ánh nến sắp tàn… cho đến khi họ cũng biến mất khỏi thế giới này.
-Exoswarm cũng không khá hơn. Những bộ phận bị chúng nuốt chửng, bị sức mạnh của Threnodian biến đổi, tái cấu trúc thành những hình thù kinh hoàng mà chúng ta gọi là Giun Hư Không. Đối với người dân Lahai-Roi, Void Storm là một thảm họa không thể đoán trước. Nơi nó tràn qua, thế giới chìm vào im lặng, chỉ còn lại hư không.
-Việc làm sáng tỏ bản chất của Void Storm chắc chắn là một bước đột phá vĩ đại. Nhưng nó cũng đặt ra cho chúng ta một thách thức to lớn không kém.
+Exoswarm cũng không khá hơn. Những bộ phận bị chúng nuốt chửng, bị sức mạnh của Threnodian biến đổi, tái cấu trúc thành những hình thù kinh hoàng mà chúng ta gọi là Giun Hư Không. Đối với người dân Lahai-Roi, Bão Hư Không là một thảm họa không thể đoán trước. Nơi nó tràn qua, thế giới chìm vào im lặng, chỉ còn lại hư không.
+Việc làm sáng tỏ bản chất của Bão Hư Không chắc chắn là một bước đột phá vĩ đại. Nhưng nó cũng đặt ra cho chúng ta một thách thức to lớn không kém.
 Hành trình khám phá những điều chưa biết của nhân loại tràn đầy vinh quang, nhưng cũng chìm trong bóng tối của rủi ro và hy sinh khổng lồ. Dù vậy, lòng dũng cảm và lý tưởng của những người dám đối mặt với cái chưa biết vẫn được khắc sâu trên đài tưởng niệm của hành trình khám phá nhân loại. Chúng nhắc nhở chúng ta về sự nhỏ bé trước thảm họa, và chứng minh ý nghĩa thực sự của lòng dũng cảm: tiếp tục tiến lên, dù biết trước nguy hiểm. Nhân loại chưa bao giờ, và sẽ không bao giờ, dừng bước vì sợ hãi.
 Roald, Koki, Mingxia, Beverly, và Bajcetic.
 Những cái tên này sẽ mãi mãi lưu lại trên vùng đất băng giá, tỏa sáng như những vì sao xuyên qua đêm cực vĩnh cửu.
@@ -9542,12 +9542,12 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Hệ thống Lịch Kép Roya: Phần I
+          <t>Hệ Thống Lịch Kép Roya: Phần I
 Người Roya duy trì hai hệ thống lịch riêng biệt: Lịch Baldur cho cuộc sống hàng ngày và Lịch Sol cho các nghi lễ.
-Lịch Baldur bắt nguồn từ việc quan sát lâu dài của người Roya đối với Reactor Drive. Bằng cách theo dõi bốn trạng thái sắc màu của Core, họ chia mỗi ngày thành ngày vàng và đêm tối, mỗi năm thành Năm Bình Yên Bluedeep và Năm Bão Tố Redheave. Do lịch này phản ánh sự biến động trong trạng thái hoạt động của Core, nó đã được người Roya áp dụng rộng rãi để hướng dẫn nông nghiệp, chăn nuôi và mọi hình thức sản xuất.
+Lịch Baldur bắt nguồn từ việc quan sát lâu dài của người Roya đối với Reactor Drive. Bằng cách theo dõi bốn trạng thái sắc màu của Lõi, họ chia mỗi ngày thành ngày vàng và đêm tối, mỗi năm thành Năm Bình Yên Bluedeep và Năm Bão Tố Redheave. Do lịch này phản ánh sự biến động trong trạng thái hoạt động của Lõi, nó đã được người Roya áp dụng rộng rãi để hướng dẫn nông nghiệp, chăn nuôi và mọi hình thức sản xuất.
 Ngược lại, Lịch Sol được coi là một trong những phát minh vĩ đại nhất của người Roya. Nó ra đời từ những quan sát cổ xưa về quỹ đạo mặt trời, từ thời họ còn sống trên mặt đất. Vào thời đó, nó dẫn đường cho những cuộc di cư đường dài của họ. Ngày nay, dù nhịp điệu của nó ít liên quan đến cuộc sống dưới lòng đất, người Roya vẫn bảo tồn nó cho các nghi lễ và tín ngưỡng.
 Theo điều tra của tác giả, dù đã rời bỏ mặt đất và sống dưới lòng đất qua nhiều thế hệ, Lịch Sol hiện chỉ lệch vài ngày so với Lịch Tiêu Chuẩn Solaris. Nói cách khác, độ chính xác thiên văn mà người Roya cổ đại đạt được đã vô cùng đáng kinh ngạc.
-Hệ thống Lịch Kép Roya: Phần II
+Hệ Thống Lịch Kép Roya: Phần II
 Lịch Baldur và Lịch Sol không chỉ khác nhau về số ngày trong năm, mà còn về tần suất chu kỳ năm. Tuy nhiên, qua những khoảng thời gian dài, hai lịch này chắc chắn sẽ trùng ngày với nhau—khoảnh khắc được thần thoại Trine của người Roya gọi là ngày một kỷ nguyên kết thúc và kỷ nguyên mới bắt đầu.
 Theo quan sát từ Solisylum, những ngày cuối cùng của Kỷ Nguyên Thứ Hai đã bắt đầu chồng lấn với bình minh của Kỷ Nguyên Thứ Ba.</t>
         </is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Rover Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Hướng&lt;/color&gt;. Khi kích hoạt, số lượng Rover Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Vận Mệnh Giả Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Hướng&lt;/color&gt;. Khi kích hoạt, số lượng Vận Mệnh Giả Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Touch để thu thập hoặc dùng Grapple tiếp cận nhanh các Băng Ghi Lời Cuối rải rác khắp Lahai-Roi.
+          <t>Chạm để thu thập hoặc dùng Móc Câu tiếp cận nhanh các Băng Ghi Lời Cuối rải rác khắp Lahai-Roi.
 Arsenio dùng thiết bị của mình để thanh tẩy ô nhiễm Vật Chất Hư Không, khôi phục lại giọng nói của những người đã khuất như bằng chứng cho sự tồn tại của họ.</t>
         </is>
       </c>
@@ -9747,8 +9747,8 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Một số Soliskin đã mất đi sự dẫn dắt của Shepherd và giờ đây lang thang ở Lahai-Roi.
-Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Soliseed Plains. Tại đó, Giant Soliskin sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Solvein Canopy, giúp những Soliskin mới được sinh ra.</t>
+          <t>Một số Soliskin đã mất đi sự dẫn dắt của Người Chăn Cừu và giờ đây lang thang ở Lahai-Roi.
+Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Đồng Bằng Soliseed. Tại đó, Soliskin Khổng Lồ sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Vòm Solvein, giúp những Soliskin mới được sinh ra.</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Void Storm cuốn phăng mọi thứ trong cơn thịnh nộ. Trong sự im lặng sau đó, những tần số ma quái của Vật Chất Hư Không là dấu vết duy nhất còn sót lại...</t>
+          <t>Bão Hư Không cuốn phăng mọi thứ trong cơn thịnh nộ. Trong sự im lặng sau đó, những tần số ma quái của Vật Chất Hư Không là dấu vết duy nhất còn sót lại...</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Minna vừa mua chiếc Terminal đầu tiên trong đời, nhưng cô bé dường như chẳng biết dùng nó như thế nào...
+          <t>Minna vừa mua chiếc Thiết bị đầu cuối đầu tiên trong đời, nhưng cô bé dường như chẳng biết dùng nó như thế nào...
 Hãy tìm gặp cô ở Bjartr Woods và giúp đỡ trước khi cô vô tình làm hỏng nó.</t>
         </is>
       </c>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Cậu đã thu hút sự chú ý của một trợ lý Terminal cực kỳ tinh ý. Hắn ta khẳng định có một đường đua mà chưa ai từng cán đích...</t>
+          <t>Cậu đã thu hút sự chú ý của một trợ lý Thiết bị đầu cuối cực kỳ tinh ý. Hắn ta khẳng định có một đường đua mà chưa ai từng cán đích...</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} trong lựa chọn hiện tại đã {Cus:Sap,S=có P=có SapTag=0} thuộc tính chính này. {Cus:Sap,S=Nó P=Chúng SapTag=0} sẽ bị bỏ qua.
+          <t xml:space="preserve">&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} trong lựa chọn hiện tại đã {Cus:Sap,S=có P=có SapTag=0} thuộc tính chính này. {Cus:Sap,S=Nó P=Chúng SapTag=0} sẽ bị bỏ qua.
 </t>
         </is>
       </c>
@@ -10081,8 +10081,8 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Phân tích mẫu sóng Rabelle cho thấy dạng dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả test nằm trong ngưỡng bình thường. 
-Kết luận: Mức Độ Tới Hạn Cộng Hưởng nằm trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Không có tiền sử cũng như nguy cơ hiện tại về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; vẫn ổn định.
+          <t>Phân tích mẫu sóng Rabelle cho thấy dạng dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả kiểm tra nằm trong ngưỡng bình thường. 
+Kết luận: Mức Độ Tới Hạn Cộng Hưởng nằm trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Không có tiền sử cũng như nguy cơ hiện tại về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; vẫn ổn định.
 Hiện tại không cần tư vấn tâm lý.
 &lt;i&gt;"Aemeath… năm học này em ấy tiến bộ tốt lắm. Nhưng chúng ta vẫn phải theo dõi sát đường cơ sở tâm lý của em. Nếu có biến động, phải can thiệp trị liệu ngay."&lt;/i&gt;
 &lt;i&gt;"Nhưng… em ấy lúc nào cũng vui vẻ thế mà?"&lt;/i&gt;
@@ -10152,7 +10152,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Bác sĩ phụ trách Khoa Điều dưỡng Resonator của Startorch Academy, nổi tiếng với trí tuệ sắc bén và sự điềm tĩnh không gì lay chuyển. Người ta đồn rằng chưa ai từng thấy ông mất bình tĩnh.
+          <t>Bác sĩ phụ trách Khoa Điều dưỡng Resonator của Học viện Startorch, nổi tiếng với trí tuệ sắc bén và sự điềm tĩnh không gì lay chuyển. Người ta đồn rằng chưa ai từng thấy ông mất bình tĩnh.
 Ông là một người lắng nghe tài ba, luôn biết cách mổ xẻ những bóng tối trong lòng người khác. Từ vết thương không lành trên tay, máu vàng rỉ ra – một chất lỏng mà ông có thể triệu hồi thành lưỡi kiếm sắc bén nhất.</t>
         </is>
       </c>
@@ -10224,8 +10224,8 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Đã tiến hành phân tích: Test Độ Stability Dao Động &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt;
-Result: Mẫu thử nghiệm Rabelle's Curve thể hiện dạng sóng elip kéo dài với biên độ đáng kể. Tuy nhiên, nhịp tuần hoàn rõ ràng được quan sát, và ngưỡng Cộng Hưởng Tới Hạn chưa bị chạm tới.
+          <t>Đã tiến hành phân tích: Kiểm tra Độ Ổn Định Dao Động &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt;
+Kết quả: Mẫu thử nghiệm Đường Cong Rabelle thể hiện dạng sóng elip kéo dài với biên độ đáng kể. Tuy nhiên, nhịp tuần hoàn rõ ràng được quan sát, và ngưỡng Cộng Hưởng Tới Hạn chưa bị chạm tới.
 Đánh giá: Chủ thể thể hiện khả năng kiểm soát ổn định dưới điều kiện tải cao, dữ liệu cho thấy khả năng tự điều chỉnh và tập trung tinh thần vượt trội. Không có dấu hiệu mất kiểm soát nào được ghi nhận.
 Kết luận: Độ ổn định của chủ thể ở mức xuất sắc. Hiện không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. Tư vấn tâm lý hiện được xem là không cần thiết. Đề xuất theo dõi định kỳ với việc tiếp tục giám sát chỉ số mệt mỏi thần kinh.
 Chủ thể đã bày tỏ sự sẵn sàng hợp tác với các quan sát tiếp theo.
@@ -10297,9 +10297,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Khoa Học Viễn Tưởng: Katya VI là một tác phẩm kinh điển tuyệt đối trong lòng người chơi trên khắp &lt;te href=850079&gt;Solaris&lt;/te&gt;. Nổi tiếng với trải nghiệm nhập vai sâu sắc và hệ thống chiến đấu tinh tế, trò chơi mời gọi người chơi bước vào cuộc hành trình của một anh hùng cô độc, chiêu mộ những người đồng hành đa dạng để chống lại cái ác đang lan tràn khắp vũ trụ.
-Ngoài cốt truyện và các trận chiến hoành tráng, trò chơi yêu thích nhất của Aemeath là một trò chơi nhỏ ẩn dạng trứng Phục sinh. Sau khi hoàn thành cốt truyện chính, cô thường quay lại chơi trò này cùng gia đình trong căn cabin của họ.
-&lt;i&gt;"Haha! Nhìn tôi này, tôi đứng thứ nhất trên bảng xếp hạng xếp khối đó!"&lt;/i&gt;</t>
+          <t>Không Gian Huyền Ảo: Katya VI là một tuyệt tác được người chơi khắp &lt;te href=850079&gt;Solaris&lt;/te&gt; yêu thích. Với trải nghiệm nhập vai sâu sắc và hệ thống chiến đấu tinh tế, trò chơi đưa người chơi vào hành trình của một anh hùng cô độc, chiêu mộ những người đồng hành đa dạng để chống lại cái ác đang lan tràn khắp vũ trụ.</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10434,7 @@
       <c r="M145" t="inlineStr">
         <is>
           <t>Aemeath ngồi trên mái một tòa nhà của Học viện, thả hồn theo làn gió nhẹ.
-Cô đã gấp vô số máy bay giấy, nhưng luôn nhớ về chiếc đầu tiên từ căn nhà gỗ. Ánh chiều xuyên qua khung cửa sổ, gió lạnh và tuyết vẫn bị chặn lại bên ngoài. Chỉ có tiếng lửa reo trong lò sưởi hòa quyện với hương thơm đậm đà của món hầm đang nấu cho bữa tối. Bên cạnh cô, người mà cô gọi là gia đình khéo léo gấp một chiếc máy bay, chiếc máy bay được tạo ra để bay thật xa. Aemeath ngước lên và thấy {Male=anh ấy;Female=cô ấy} mỉm cười khi {Male=anh ấy;Female=cô ấy} đưa chiếc máy bay hoàn thành cho cô.
+Cô đã gấp vô số máy bay giấy, nhưng luôn nhớ về chiếc đầu tiên từ căn nhà gỗ. Ánh chiều xuyên qua khung cửa sổ, gió lạnh và tuyết vẫn bị chặn lại bên ngoài. Chỉ có tiếng lửa reo trong lò sưởi hòa quyện với hương thơm đậm đà của món hầm đang nấu cho bữa tối. Bên cạnh cô, người mà cô gọi là gia đình khéo léo gấp một chiếc máy bay, chiếc máy bay được tạo ra để bay thật xa. Aemeath ngước lên và thấy {Male=he;Female=she} mỉm cười khi {Male=he;Female=she} đưa chiếc máy bay hoàn thành cho cô.
 Khung cảnh dần tan vào màn sương ký ức, chỉ còn lại cảnh quan Học viện trước mắt. Với nụ cười nhẹ, Aemeath thả chiếc máy bay giấy mới gấp của mình theo làn gió.</t>
         </is>
       </c>
@@ -10572,7 +10570,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Một đôi găng tay y tế trắng tinh. Chúng che giấu &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của anh và vết thương cũ không bao giờ lành, nơi chảy ra thứ máu vàng mà anh gọi là "Ichor".
+          <t>Một đôi găng tay y tế trắng tinh. Chúng che giấu &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của anh và vết thương cũ không bao giờ lành, nơi chảy ra thứ máu vàng mà anh gọi là "Ichor".
 Với anh, thứ máu này là nguồn sức mạnh. Nhưng với người khác, nó là mối nguy hiểm bỏng rát. Vì vậy, anh giấu đi ánh sáng đó, cùng với lịch sử mà nó đại diện, kín đáo dưới lớp vải trắng muốt.</t>
         </is>
       </c>
@@ -10640,7 +10638,7 @@
       <c r="M148" t="inlineStr">
         <is>
           <t>Kẹp giữa những trang sách trên bàn làm việc là một tờ giấy gói kẹo, mép đã hơi quăn lại. In trên đó là hình "Sunshine Bear" – một thiết kế đã ngừng sản xuất từ lâu. Hồi còn nhỏ, cha cậu thường thưởng cho cậu chiếc kẹo này.
-Giờ thì người đàn ông ấy đã mất. Ngôi nhà ấy cũng không còn. Chiếc kẹo ấy cũng không còn được sản xuất nữa. Cậu vuốt phẳng tờ giấy gói đã phai màu và dùng nó làm điểm đánh dấu, Dodgen lại cả một tuổi thơ đầy xung đột và đau khổ vào một thứ mong manh nhưng đủ kiên cường để lặng lẽ trượt giữa những trang ký ức.</t>
+Giờ thì người đàn ông ấy đã mất. Ngôi nhà ấy cũng không còn. Chiếc kẹo ấy cũng không còn được sản xuất nữa. Cậu vuốt phẳng tờ giấy gói đã phai màu và dùng nó làm điểm đánh dấu, nén lại cả một tuổi thơ đầy xung đột và đau khổ vào một thứ mong manh nhưng đủ kiên cường để lặng lẽ trượt giữa những trang ký ức.</t>
         </is>
       </c>
     </row>
@@ -10725,18 +10723,18 @@
 Mái tóc đỏ rực của Alara dường như mất đi chút ánh hào quang khi cô thốt lên một tiếng rên yếu ớt: "Trời... đồ ăn căng tin giờ chẳng còn ngon nữa!" Bên cạnh, Nova vẫn cần mẫn xúc từng thìa thứ gì đó không thể nhận dạng nổi, bình thản nhận xét: "Đúng vậy, cô nàng. Điểm số thì đau thật đấy. Nhưng thẳng thắn mà nói, đồ ăn ở đây chưa bao giờ ngon cả." Lynn trông như sụp đổ hoàn toàn vì kết quả của mình, còn Celeste thì nhẹ nhàng an ủi cô. Riêng Aemeath, cô lại mang vẻ mặt xa xăm, lơ đãng nhấm nháp Squeezy Jelly vị tự chế, trò chuyện vu vơ với mấy người bạn &lt;te href=700009&gt;Synchronist&lt;/te&gt;.
 Bỗng nhiên, Alara quay sang cô.
 "Aemeath! Sao cậu có vẻ chẳng lo lắng gì thế?"
-Aemeath chớp mắt. "Lo lắng về cái gì?... À, điểm số à?" Cô dừng lại, rồi vung tay một cách hờ hững. "Nhưng lần này điểm của mọi người cũng chẳng khác nhau là mấy mà. Professor Sakya chỉ quá khắt khe thôi. Chứ có phải tụi mình tệ đâu. Cứ thoải mái đi." Cô rút một tờ khăn giấy ra, dúi cho cô bạn hay khóc nhất nhóm. "Này, Lynn! Mau lau nước mắt đi!"
+Aemeath chớp mắt. "Lo lắng về cái gì?... À, điểm số à?" Cô dừng lại, rồi vung tay một cách hờ hững. "Nhưng lần này điểm của mọi người cũng chẳng khác nhau là mấy mà. Giáo sư Sakya chỉ quá khắt khe thôi. Chứ có phải tụi mình tệ đâu. Cứ thoải mái đi." Cô rút một tờ khăn giấy ra, dúi cho cô bạn hay khóc nhất nhóm. "Này, Lynn! Mau lau nước mắt đi!"
 Celeste đưa khăn giấy cho Lynn, trao đổi ánh mắt với mọi người rồi nhẹ nhàng nói: "Cậu thực sự chẳng quan tâm gì đến tương lai của một Synchronist à."
-Lúc này, Aemeath thường làm gì? Có lẽ sẽ pha trò, đổi chủ đề, cười trừ. Nhưng hôm nay là sinh nhật của người ấy, và hình ảnh {Male=anh;Female=cô} ấy cứ hiện lên trong đầu cô. Lần này, cô quên mất phải che giấu cảm xúc trước bạn bè.
-"Làm một Synchronist... cũng chỉ là một con đường thôi," cô nói đều đều. "Có người từng nói với mình {Male=anh;Female=cô} ấy mong mình được sống một cuộc đời hạnh phúc, vô tư. Mình nghĩ điều đó quan trọng hơn. Ước mơ của mình không lớn lao như các cậu. Với một kẻ lười như mình, sống nhẹ nhàng có gì là sai?"
-"Thật sự à?" đám bạn hỏi, nhìn cô chăm chú.
-Aemeath chỉ mỉm cười đáp lại. "Thật sự mà."
+Lúc này, Aemeath thường làm gì? Có lẽ sẽ pha trò, đổi chủ đề, cười trừ. Nhưng hôm nay là sinh nhật của người ấy, và hình ảnh {Male=he;Female=she} ấy cứ hiện lên trong đầu cô. Lần này, cô quên mất phải che giấu cảm xúc trước bạn bè.
+"Làm một Synchronist... cũng chỉ là một con đường thôi," cô nói đều đều. "Có người từng nói với mình {Male=he;Female=she} ấy mong mình được sống một cuộc đời hạnh phúc, vô tư. Mình nghĩ điều đó quan trọng hơn. Ước mơ của mình không lớn lao như các cậu. Với một kẻ lười như mình, sống nhẹ nhàng có gì là sai?"
+"Thật à?" đám bạn hỏi, nhìn cô chăm chú.
+Aemeath chỉ mỉm cười đáp lại. "Thật mà."
 Nhưng đó không phải sự thật.
-Ước mơ thực sự của cô quá nặng nề, quá ngạo mạn, quá phi lý để có thể thốt ra bằng những lời lẽ điềm tĩnh. Nó lớn dần lên mỗi ngày, bám rễ sâu vào trái tim cô. Nhưng cô từ chối thừa nhận nó, bởi cô đã chấp nhận lời hứa ấy. Nếu ngày nào cũng chỉ cần hạnh phúc đơn giản thế này là đủ, thì cô sẽ mãi hạnh phúc như vậy. Cô sẽ giữ lời mình. Unless...
+Ước mơ thực sự của cô quá nặng nề, quá ngạo mạn, quá phi lý để có thể thốt ra bằng những lời lẽ điềm tĩnh. Nó lớn dần lên mỗi ngày, bám rễ sâu vào trái tim cô. Nhưng cô từ chối thừa nhận nó, bởi cô đã chấp nhận lời hứa ấy. Nếu ngày nào cũng chỉ cần hạnh phúc đơn giản thế này là đủ, thì cô sẽ mãi hạnh phúc như vậy. Cô sẽ giữ lời mình. Trừ khi...
 Suy nghĩ của cô bị gián đoạn đột ngột khi Alara bóp mạnh vào má cô.
 "Au! Làm gì thế?" Aemeath kêu lên, giọng nghẹn.
 "Con bé dối trá," cô bạn càu nhàu. "Thôi được, thôi được. Chúng ta không hỏi nữa... Chiều nay đi thư viện không? Học nhóm đi?"
-Aemeath gật đầu. "Of course!"
+Aemeath gật đầu. "Tất nhiên rồi!"
 Cười đùa, xô đẩy nhau, Aemeath cùng đám bạn tiến về phía thang máy. Họ đều còn trẻ, chẳng vội gì tìm câu trả lời. Trong ngôi trường này đầy rẫy những thiên tài, tương lai vẫn còn trải dài trước mắt, đầy những khả năng vô tận.</t>
         </is>
       </c>
@@ -10818,16 +10816,16 @@
           <t>Chỉ có sự tĩnh lặng.
 Aemeath quay lại và nhìn thấy nó.
 Nó giống như một con mắt, nhưng cô biết đó không phải. Một hố đen? Có lẽ đó là khái niệm gần nhất mà con người có thể nghĩ ra. Nhưng với người cộng hưởng với &lt;te href=700008&gt;Exostrider&lt;/te&gt;, đó là một trật tự tồn tại khác: một "hiện tượng" của sự xảy ra không ngừng, tràn đầy. Bất cứ thứ gì bị nó nuốt chửng đều đơn giản là biến mất. &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; gọi nó là Vật Chất Hư Không. Hãy cứ gọi nó như vậy. Những sinh vật ở chiều không gian thấp hơn cần một thuật ngữ cho nó, cũng như con người cần gọi cái "mắt" đó là Aleph-1.
-Đây không phải lần đầu cô gặp cái gọi là "ánh nhìn" của nó. Những cuộc chạm trán như vậy là không thể tránh khỏi trong những chuyến du hành lặp đi lặp lại của cô giữa Space Hư Không và thế giới bên ngoài. Theo thời gian, cô đã học cách không phản ứng.
+Đây không phải lần đầu cô gặp cái gọi là "ánh nhìn" của nó. Những cuộc chạm trán như vậy là không thể tránh khỏi trong những chuyến du hành lặp đi lặp lại của cô giữa Không Gian Hư Không và thế giới bên ngoài. Theo thời gian, cô đã học cách không phản ứng.
 Cho đến cách đây không lâu, ánh nhìn của nó luôn ảnh hưởng đến cô. Một sự trống rỗng. Một mong muốn lặng lẽ tan biến. Cảm giác rằng không gì có ý nghĩa trước một vũ trụ im lặng, không hồi đáp. Đó là những hậu quả của việc nhìn vào Aleph-1 mà ngay cả cái chết cũng không giải thoát được cô. Nhưng giờ đây, sau khi khám phá những tàn tích của một trong những nền văn minh bị nó nuốt chửng, cô nhìn vào con mắt vô tận vượt thời gian và không gian đó và chỉ nghe thấy tiếng cười của chính mình, mỏng manh và gần như điên loạn.
-"Vậy đây là thứ {Male=anh ấy;Female=cô ấy} tìm kiếm sao?"
+"Vậy đây là thứ {Male=him;Female=her} tìm kiếm sao?"
 Tiếng cười thoát ra khỏi cô thật giòn tan.
 "Đây là... sự thật sao?"
 Thật nực cười.
 Mọi lý tưởng và tầm nhìn được nuôi dưỡng từ thuở ấu thơ đều sụp đổ cùng một lúc, trở nên trống rỗng ý nghĩa. Aemeath kiệt sức. Dưới sự mệt mỏi ấy, một nỗi đau âm ỉ trỗi dậy, theo sau là thứ gì đó lạnh lẽo hơn.
-"Còn {Male=anh ấy;Female=cô ấy} thì sao?"
-"{Male=Anh ấy;Female:Cô ấy} có biết không?"
-Nếu {Male=anh ấy;Female=cô ấy} biết, Aemeath không thể tưởng tượng {Male=anh ấy;Female=cô ấy} đã tiếp tục tiến lên như thế nào với gánh nặng này. Còn nếu {Male=anh ấy;Female=cô ấy} không biết... thì sự thật này sẽ không bao giờ được đến tai {Male=anh ấy;Female:cô ấy}. Nó phải bị chôn vùi. Phá vỡ. Xóa sạch hoàn toàn. Một mối lo lạnh lẽo đọng lại trong tim cô, ngay cả khi nó bừng cháy bởi một cơn thịnh nộ thuần khiết, sáng rõ. Lần đầu tiên, cô hiểu thế nào là sự căm ghét.
+"Còn {Male=him;Female=her} thì sao?"
+"{Male=he;Female=she} có biết không?"
+Nếu {Male=he;Female=she} biết, Aemeath không thể tưởng tượng {Male=he;Female=she} đã tiếp tục tiến lên như thế nào với gánh nặng này. Còn nếu {Male=he;Female=she} không biết... thì sự thật này sẽ không bao giờ được đến tai {Male=him;Female=her}. Nó phải bị chôn vùi. Phá vỡ. Xóa sạch hoàn toàn. Một mối lo lạnh lẽo đọng lại trong tim cô, ngay cả khi nó bừng cháy bởi một cơn thịnh nộ thuần khiết, sáng rõ. Lần đầu tiên, cô hiểu thế nào là sự căm ghét.
 Ảo ảnh chiếc máy bay giấy cô tạo ra vỡ vụn trong nắm tay. Cô buông những mảnh vụn tuột khỏi ngón tay và nhìn chúng trôi đi, tan biến vào hư không vô tận.</t>
         </is>
       </c>
@@ -10906,9 +10904,9 @@
       <c r="M151" t="inlineStr">
         <is>
           <t>Aemeath từ từ bước lên cầu thang và trở lại bàn làm việc.
-Giấc mơ đã xua tan mọi cơ hội để ngủ tiếp. Dù thực ra cô cũng chẳng cần ngủ nữa. Giấc mơ chỉ là những ký ức được phát lại theo một trật tự khác. Tomorrow, cô và {PlayerName} sẽ đứng trước Exostrider. Cô không biết điều gì sẽ xảy ra, chỉ biết mình muốn sẵn sàng.
-Lời nói là ý nghĩa được định hình. Vì vậy, cô muốn để lại điều gì đó—điều mà cô muốn nói với {Male=anh;Female=em}, nhưng vẫn chưa thể thốt ra.
-Nhưng bắt đầu từ đâu? Cô có thể kể lại tất cả những gì đã xảy ra trong những năm qua: những khoảnh khắc nhỏ bé, dễ quên, niềm vui, nỗi buồn, những ngày tháng tầm thường và những sự kiện định hình thế giới. Hoặc có lẽ cô có thể than phiền đôi chút. {Male=Anh;Female=Em} đã đi quá lâu, và những điều cô muốn chia sẻ đã chất đống, chờ đợi. Nếu tất cả những điều đó đều không phù hợp, cô luôn có thể vẽ lại chuyến đi này. Như ngày xưa.
+Giấc mơ đã xua tan mọi cơ hội để ngủ tiếp. Dù thực ra cô cũng chẳng cần ngủ nữa. Giấc mơ chỉ là những ký ức được phát lại theo một trật tự khác. Ngày mai, cô và {PlayerName} sẽ đứng trước Exostrider. Cô không biết điều gì sẽ xảy ra, chỉ biết mình muốn sẵn sàng.
+Lời nói là ý nghĩa được định hình. Vì vậy, cô muốn để lại điều gì đó—điều mà cô muốn nói với {Male=He;Female=She}, nhưng vẫn chưa thể thốt ra.
+Nhưng bắt đầu từ đâu? Cô có thể kể lại tất cả những gì đã xảy ra trong những năm qua: những khoảnh khắc nhỏ bé, dễ quên, niềm vui, nỗi buồn, những ngày tháng tầm thường và những sự kiện định hình thế giới. Hoặc có lẽ cô có thể than phiền đôi chút. {Male=He;Female=She} đã đi quá lâu, và những điều cô muốn chia sẻ đã chất đống, chờ đợi. Nếu tất cả những điều đó đều không phù hợp, cô luôn có thể vẽ lại chuyến đi này. Như ngày xưa.
 Cô gõ phím. Xóa đi. Rồi gõ lại. Cuối cùng, chỉ còn một dòng duy nhất.
 "Tôi biết rằng nếu ngước nhìn lên, ngôi sao đó sẽ luôn tìm thấy tôi."
 Cô lưu tin nhắn vào một thiết bị trong phòng, để lại cho một tương lai có thể được phát hiện, hoặc có thể sẽ chẳng bao giờ ai biết.
@@ -11089,8 +11087,8 @@
 Đêm khuya, một mình, Luuk tháo găng tay và nhìn Ichor chảy ra từ lòng bàn tay. Dòng máu vàng tràn trên da, kết tụ thành hình lưỡi dao cứng cáp. Rồi chỉ với một cái xoay cổ tay, nó lại tan biến thành chất lỏng ngoan ngoãn.
 Sau bao năm, "sự thay đổi" mà cha cậu từng ám ảnh cuối cùng đã xuất hiện. Và nó nghe lời cậu.
 "Nhưng ta đã chán việc hy sinh người khác cho ngươi rồi," cậu lẩm bẩm, mắt dán chặt vào ánh vàng lấp lánh. "Ta sẽ... sử dụng ngươi."
-"Xâm nhập Fractsidus?" Giọng từ Terminal rõ ràng run rẩy.
-"Yes." Luuk đứng bên rìa mái nhà, gió thổi tung áo khoác. "Quá nhiều manh mối dẫn về chúng. Ta nghi ngờ chúng có liên quan đến cái chết của cha ta."
+"Xâm nhập Fractsidus?" Giọng từ Thiết bị đầu cuối rõ ràng run rẩy.
+"Đúng vậy." Luuk đứng bên rìa mái nhà, gió thổi tung áo khoác. "Quá nhiều manh mối dẫn về chúng. Ta nghi ngờ chúng có liên quan đến cái chết của cha ta."
 "...Cậu đã suy nghĩ kỹ chưa? Một khi đã vào, sẽ không thể quay lại."
 Luuk nhìn xuống những ánh đèn lấp lánh bên dưới. Bao nhiêu sinh mạng, chỉ được duy trì bằng thuốc men, le lói như ngọn nến trong gió, chờ đợi qua đêm dài vô tận cho đến khi ảo ảnh tan biến và bình minh cuối cùng cũng đến?
 "Không thể quay lại," cậu nói rồi lao vào màn đêm, giọng cậu tan biến trong gió, "Đó mới là lý do đáng để làm."</t>
@@ -11184,7 +11182,7 @@
 Luuk khom người, cúi đầu, bước nhanh hơn cho đến khi dường như thu mình vào chiếc áo blouse trắng.
 Chiếc túi y tế mở ra với tiếng tách nhẹ. Anh cẩn thận lấy kẹp và bông gạc sát trùng, bắt đầu lau vết thương trên cánh tay một người. Ở góc phòng, vài người ít thương hơn thì thầm với nhau.
 "Suỵt!" Ai đó ngắt lời gằn giọng, mắt liếc lo lắng về phía Luuk đang làm việc.
-Người nói ngừng lại một thoáng, rồi khinh khỉnh. "Lo gì chứ? Hắn à?" Giọng anh ta cố tình to hơn. "Lần trước hắn băng bó vai ta, sợ đến mức thở hổn hển. Nhìn kìa, nhát như thỏ đế. Chả làm nên trò trống gì đâu."
+Người nói ngừng lại một thoáng, rồi khinh khỉnh. "Lo gì chứ? Hắn à?" Giọng anh ta cố tình to hơn. "Lần trước hắn băng bó vai tao, sợ đến mức thở hổn hển. Nhìn kìa, nhát như thỏ đế. Chả làm nên trò trống gì đâu."
 Đúng lúc đó, Luuk đẩy gọng kính lên sống mũi. Ánh mắt vẫn cúi xuống, tập trung hoàn toàn vào miếng băng trong tay như thể chẳng nghe thấy gì.
 "Dù sao cũng cẩn thận vẫn hơn," ai đó lẩm bẩm. "Tất cả tiền đồn đều báo động cao. Nghe nói có con chuột đã lọt vào..."
 Giọng họ nhỏ dần thành tiếng thì thầm mơ hồ. Luuk vẫn giữ tư thế vô hại, nhưng đôi tay không bao giờ mất đi sự chính xác. Sát trùng, bôi thuốc, băng bó, từng bước thực hiện hoàn hảo. Chỉ đôi khi anh để lộ chút căng thẳng: tiếng kẹp kim loại va chạm nhẹ, nắp lọ thuốc tuột khỏi tay một hai lần.
@@ -13836,7 +13834,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Platya, người mang Bình Minh Bờ Đen, đã đến Startorch Academy vì tin đồn về một Ghost Miko—những lời thì thầm dường như vang vọng truyền thuyết về "Nữ Miko" từ quê hương xa xôi của cô. Tò mò, cậu quyết định cùng cô tìm hiểu.</t>
+          <t>Platya, người mang Bình Minh Bờ Đen, đã đến Học viện Startorch vì tin đồn về một Ghost Miko—những lời thì thầm dường như vang vọng truyền thuyết về "Nữ Miko" từ quê hương xa xôi của cô. Tò mò, cậu quyết định cùng cô tìm hiểu.</t>
         </is>
       </c>
     </row>
@@ -13915,16 +13913,16 @@
         <is>
           <t>...
 Mãi đến nửa đêm, con tàu vượt biển mới vượt qua được Khu Giám Sát Bão Vô Hình và tiến gần đến vùng Roya Frostlands băng giá.
-Ngoài ô cửa sổ, xuyên qua màn sương biển mỏng manh, một vách đá băng trải dài vô tận hiện ra. Ta không rời mắt khỏi chúng, hơi thở vô thức gấp gáp khi bức "tường trắng" khổng lồ dần áp sát. Cho đến lúc này, vùng đất băng giá chỉ là những dòng tiêu đề xa lạ, và Tập Đoàn Cực Bắc đa quốc gia vẫn là điều gì đó xa vời. Nhưng giờ đây, chúng đang ở ngay trước mắt. Thông báo cập bến hòa cùng tiếng rên rỉ của tời neo và sức căng của dây cáp, báo hiệu ta đã đến Roya Icebreak Port.
+Ngoài ô cửa sổ, xuyên qua màn sương biển mỏng manh, một vách đá băng trải dài vô tận hiện ra. Ta không rời mắt khỏi chúng, hơi thở vô thức gấp gáp khi bức "tường trắng" khổng lồ dần áp sát. Cho đến lúc này, vùng đất băng giá chỉ là những dòng tiêu đề xa lạ, và Tập Đoàn Cực Bắc đa quốc gia vẫn là điều gì đó xa vời. Nhưng giờ đây, chúng đang ở ngay trước mắt. Thông báo cập bến hòa cùng tiếng rên rỉ của tời neo và sức căng của dây cáp, báo hiệu ta đã đến Cảng Phá Băng Roya.
 Sau vài vòng kiểm tra nghiêm ngặt, ta nhập đoàn với nhóm nghiên cứu và rời cảng. Cùng nhau, chúng ta bước lên thang máy chuyển tiếp hướng về khu vực trung tâm của vùng băng giá. Chiếc thang đủ rộng để chở đủ nhu yếu phẩm duy trì một trạm nghiên cứu nhỏ trong sáu tháng. Nhưng chỉ hai phút sau khi bắt đầu leo lên, cảm giác về tỷ lệ của ta hoàn toàn sụp đổ. Khi chiếc thang máy khổng lồ bò lên vách đá băng, nó giống như một con kiến đang vật lộn leo lên sườn núi.
 ...
 Với sự hỗ trợ của nhóm nghiên cứu, hành trình đến Trạm Nghiên Cứu Cực Bắc của ta diễn ra suôn sẻ. Sau khi đăng ký, đội trưởng dẫn ta đến kho chứa, nơi ta được phát tất cả những vật dụng cần thiết để sinh tồn ở vùng băng giá. Rồi ta được đưa đến phòng ở—nơi ta sẽ trải qua mỗi sáng và tối trong thời gian lưu trú.
-Ta để hành lý cá nhân ở đó và bắt đầu khám phá các cơ sở trong trạm. Có lẽ nhờ thông báo trước của Pioneer Association đến các nhà nghiên cứu, ta có thể di chuyển qua hầu hết các khu vực trong trạm mà không gặp trở ngại, ngoại trừ một vài khu vực hạn chế. Theo những gì ta thấy, Giai Đoạn Một của dự án xây dựng Tập Đoàn Cực Bắc—cụ thể là Cảng Vận Chuyển Frostlands—đã hoàn thành hoàn toàn. Theo các nhà nghiên cứu, cư dân bản địa, người Roya, cùng với đàn Exoswarm mà họ chăn nuôi, đã đóng vai trò quan trọng trong quá trình xây dựng.
-Tuy nhiên, khi ta hỏi về kế hoạch cho Giai Đoạn Hai, không ai đưa ra câu trả lời rõ ràng. Hầu hết nhân viên đều bận rộn với công việc nghiên cứu và xây dựng của riêng họ. Dù không ai nói thẳng, nhưng biểu cảm của họ đã nói lên tất cả: họ không có thời gian cho một "khách viếng thăm" từ Pioneer Association.
+Ta để hành lý cá nhân ở đó và bắt đầu khám phá các cơ sở trong trạm. Có lẽ nhờ thông báo trước của Hiệp Hội Tiên Phong đến các nhà nghiên cứu, ta có thể di chuyển qua hầu hết các khu vực trong trạm mà không gặp trở ngại, ngoại trừ một vài khu vực hạn chế. Theo những gì ta thấy, Giai Đoạn Một của dự án xây dựng Tập Đoàn Cực Bắc—cụ thể là Cảng Vận Chuyển Frostlands—đã hoàn thành hoàn toàn. Theo các nhà nghiên cứu, cư dân bản địa, người Roya, cùng với đàn Exoswarm mà họ chăn nuôi, đã đóng vai trò quan trọng trong quá trình xây dựng.
+Tuy nhiên, khi ta hỏi về kế hoạch cho Giai Đoạn Hai, không ai đưa ra câu trả lời rõ ràng. Hầu hết nhân viên đều bận rộn với công việc nghiên cứu và xây dựng của riêng họ. Dù không ai nói thẳng, nhưng biểu cảm của họ đã nói lên tất cả: họ không có thời gian cho một "khách viếng thăm" từ Hiệp Hội Tiên Phong.
 ...
 Theo quan sát của ta, trạm nghiên cứu đã nhận tổng cộng chín mươi hai xe tải trong ba ngày qua. Trong số hàng hóa đó, chỉ một phần rất nhỏ được phân phối đến các khu vực khác trong vùng băng giá. Phần lớn được chuyển xuống lòng đất qua hệ thống đường sắt nhẹ. Từ đó, ta kết luận rằng Giai Đoạn Hai của dự án không tập trung vào vùng băng giá, mà vào khu vực ngầm Lahai-Roi—chỉ có thể tiếp cận qua Starward Riseway.
 ...
-Ngày thứ sáu, ta thức dậy như thường lệ tại Trạm Nghiên Cứu Cực Bắc. Sau bữa sáng ở khu ăn uống, ta lại tìm gặp trưởng đoàn thám hiểm và lần thứ ba nộp đơn yêu cầu thăm Lahai-Roi. Đúng như dự đoán, yêu cầu của ta lại bị từ chối. Ta không giấu được sự thất vọng, nhưng hiểu được sự thận trọng của họ. Mọi thứ ở đây—những phát hiện, những hàm ý—đều quá kỳ lạ, quá chấn động đối với kiến thức đã được công nhận. Dù có Pioneer Association đứng sau, họ vẫn có mọi lý do để tiến hành một cách cẩn trọng.
+Ngày thứ sáu, ta thức dậy như thường lệ tại Trạm Nghiên Cứu Cực Bắc. Sau bữa sáng ở khu ăn uống, ta lại tìm gặp trưởng đoàn thám hiểm và lần thứ ba nộp đơn yêu cầu thăm Lahai-Roi. Đúng như dự đoán, yêu cầu của ta lại bị từ chối. Ta không giấu được sự thất vọng, nhưng hiểu được sự thận trọng của họ. Mọi thứ ở đây—những phát hiện, những hàm ý—đều quá kỳ lạ, quá chấn động đối với kiến thức đã được công nhận. Dù có Hiệp Hội Tiên Phong đứng sau, họ vẫn có mọi lý do để tiến hành một cách cẩn trọng.
 ...</t>
         </is>
       </c>
@@ -14033,7 +14031,7 @@
 Rời bỏ thế gian,
 Gác lại muộn phiền.
 Không sợ hãi, không nghi ngờ.
-Parents đợi với ánh mắt hy vọng,
+Cha mẹ đợi với ánh mắt hy vọng,
 Bạn cũ sum vầy.
 Những gương mặt thân quen,
 Những gương mặt thân quen.</t>
@@ -14110,12 +14108,12 @@
       <c r="M197" t="inlineStr">
         <is>
           <t>...
-Vào ngày này, đội thám hiểm của Pioneer Association lần đầu đặt chân lên vùng đất băng giá và tiếp xúc với tộc Roya – những người dẫn dắt Bầy Ngoại Lai băng qua lớp băng dày, đưa chúng trở về với Người Điều Khiển Ngoại Lai.
-Các nhà nghiên cứu nhìn những người Roya chăn dắt bầy đàn như những người chăn cừu, Dodget mặt không giấu nổi sự háo hức. Trong mắt họ, Lahai-Roi chắc chắn sẽ trở thành một trong những phát hiện vĩ đại nhất của thời đại. Còn tộc Roya, bị cô lập khỏi thế giới bên ngoài suốt vô số thế hệ, cũng quan sát những vị khách lạ mặt với vẻ tò mò không kém, lần đầu nhận thức được sự tồn tại của thế giới bên ngoài Lahai-Roi.
+Vào ngày này, đội thám hiểm của Hiệp Hội Tiên Phong lần đầu đặt chân lên vùng đất băng giá và tiếp xúc với tộc Roya – những người dẫn dắt Bầy Ngoại Lai băng qua lớp băng dày, đưa chúng trở về với Người Điều Khiển Ngoại Lai.
+Các nhà nghiên cứu nhìn những người Roya chăn dắt bầy đàn như những người chăn cừu, nét mặt không giấu nổi sự háo hức. Trong mắt họ, Lahai-Roi chắc chắn sẽ trở thành một trong những phát hiện vĩ đại nhất của thời đại. Còn tộc Roya, bị cô lập khỏi thế giới bên ngoài suốt vô số thế hệ, cũng quan sát những vị khách lạ mặt với vẻ tò mò không kém, lần đầu nhận thức được sự tồn tại của thế giới bên ngoài Lahai-Roi.
 ...
 Trên hành trình trở về, trưởng đoàn thám hiểm lập tức bắt tay soạn thảo báo cáo về Lahai-Roi, từng dòng chữ đều tràn ngập sự phấn khích và kinh ngạc. Cô tin mình đang đứng trước ngưỡng cửa lịch sử, sắp trở thành một nhà thám hiểm huyền thoại.
 “Nơi vùng cực xa xôi ấy tồn tại một nền văn minh kỳ lạ, tách biệt với thế giới. Họ là một dân tộc cổ xưa, sinh sống dưới lớp băng vĩnh cửu, trong một vương quốc rộng lớn ẩn mình. Trang phục của họ chẳng hề giống với xã hội hiện đại... Họ chăn nuôi, nhưng đàn gia súc của họ không phải máu thịt. Thay vào đó, họ dẫn dắt những đàn gia súc cơ khí, thậm chí cả những cỗ máy khổng lồ như voi...”
-Thế nhưng, khi bản báo cáo này đến tay trụ sở Pioneer Association, mọi chuyện lại diễn ra ngoài dự đoán của đoàn thám hiểm. Không có thông báo công khai, không có lễ kỷ niệm phát hiện. Thay vào đó, ngay khi trở về, cả đoàn bị giám sát nghiêm ngặt.
+Thế nhưng, khi bản báo cáo này đến tay trụ sở Hiệp Hội Tiên Phong, mọi chuyện lại diễn ra ngoài dự đoán của đoàn thám hiểm. Không có thông báo công khai, không có lễ kỷ niệm phát hiện. Thay vào đó, ngay khi trở về, cả đoàn bị giám sát nghiêm ngặt.
 Ban lãnh đạo Hiệp Hội tin rằng một “tiết lộ chấn động” như vậy có thể gây ra bất ổn khó lường.
 Cuối cùng, mọi thông tin liên quan đến Lahai-Roi đều bị niêm phong. Đoàn thám hiểm và tất cả những gì họ phát hiện đều bị coi như chưa từng tồn tại.</t>
         </is>
@@ -14430,7 +14428,7 @@
 Trong lần vận chuyển cuối cùng của ▇▇, Baldur đã chạm trán ▇▇ và trước khi đến được điểm đến dự định ▇▇▇, nó đã bị thương nặng trong cuộc chiến với ██. Baldur vẫn tiếp tục chiến đấu với ▇▇ cho đến khi đặt chân lên vùng đất mà ta đang sống hiện nay.
 Dù mối liên hệ giữa lữ khách và Baldur đã được xác nhận, thông tin này vẫn gây chấn động trong giới cầm quyền. Nhưng sau khi suy xét kỹ, không thể phớt lờ sự thật: những lời kể này trùng khớp với các đoạn trong thần thoại Roya và hoàn toàn có thể được chấp nhận là sự thật. Đây, không nghi ngờ gì nữa, chính là nguồn gốc của Baldur. Sau khi bàn bạc, Lục Hạo Thần quyết định tạm thời niêm phong những ghi chép này.
 …
-Ngày nay, Spacetrek Collective đã đi vào hoạt động hoàn toàn, và Viện Nghiên Cứu đang dần khám phá bản chất của Baldur. Có lẽ lữ khách tiết lộ nguồn gốc của Baldur cho ta là vì đã đến lúc thông tin này cần được chia sẻ rộng rãi hơn.
+Ngày nay, Spacetrek Collective đã đi vào hoạt động hoàn toàn, và Viện Nghiên cứu đang dần khám phá bản chất của Baldur. Có lẽ lữ khách tiết lộ nguồn gốc của Baldur cho ta là vì đã đến lúc thông tin này cần được chia sẻ rộng rãi hơn.
 Cầu mong kế hoạch của Spacetrek Collective diễn ra suôn sẻ… Cầu mong người khổng lồ soi sáng vùng băng giá sẽ trỗi dậy một lần nữa.</t>
         </is>
       </c>
@@ -14497,7 +14495,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sigrika, học viên của Startorch Academy và là một Resonator của Royan Runes.
+          <t>Sigrika, học viên của Học viện Startorch và là một Resonator của Royan Runes.
 Cô quyết tâm sống xứng đáng với kỳ vọng của mọi người và trở thành một Solsworn chân chính, nên luôn dốc hết sức mình cho mọi thử thách.</t>
         </is>
       </c>
@@ -14571,10 +14569,10 @@
         <is>
           <t>Phân tích mẫu dạng sóng của Rabelle cho thấy các dao động biên độ cao, không tuần hoàn. Có hiện tượng mờ dạng sóng cục bộ cùng với các dạng sóng bất thường rõ rệt. 
 Kết luận: &lt;te href=850073&gt;Đỉnh Cộng Hưởng&lt;/te&gt; vẫn nằm trong ngưỡng cho phép. Tuy nhiên, độ ổn định của đối tượng rất kém, có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; tiềm ẩn.
-Hiện tại, Resonator Sigrika chưa từng bị Quá Tải, và &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; của cô vẫn ổn định.
+Hiện tại, Resonator Sigrika chưa từng bị Quá Tải, và &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; của cô vẫn ổn định.
 Cần tiến hành tư vấn tâm lý định kỳ.
 &lt;i&gt;"Sigrika quá khắt khe với bản thân. Thật lòng mà nói, nếu cô ấy bớt gồng mình một chút, độ ổn định của Resonator sẽ cải thiện đáng kể."&lt;/i&gt;
-&lt;i&gt;"...Học viên như cô ấy không hiếm ở Startorch Academy. Họ đến đây với suy nghĩ tài năng là tất cả. Rồi mới vỡ lẽ rằng ở đây, tài năng chỉ giúp họ có lợi thế trong vài môn học. Chẳng hơn gì."&lt;/i&gt;
+&lt;i&gt;"...Học viên như cô ấy không hiếm ở Học viện Startorch. Họ đến đây với suy nghĩ tài năng là tất cả. Rồi mới vỡ lẽ rằng ở đây, tài năng chỉ giúp họ có lợi thế trong vài môn học. Chẳng hơn gì."&lt;/i&gt;
 &lt;i&gt;"Dù vậy, tôi không muốn học viên của mình bị định nghĩa bởi điểm số, tài năng hay năng lực. Họ xứng đáng được thấy thế giới này còn bao điều kỳ diệu hơn thế."&lt;/i&gt;</t>
         </is>
       </c>
@@ -14712,7 +14710,7 @@
       <c r="M205" t="inlineStr">
         <is>
           <t>Một cuốn nhật ký về chim mà Sigrika giữ, dù hầu hết các mục chỉ là những hình bóng mờ. Những bức phác họa và ghi chú tràn ngập sự hứng khởi không che giấu của người sưu tập.
-"Đứng yên nào! Đừng vẫy đuôi với ta nữa, Blubbin Puffin! Đứng yên! Đừng nhúc nhích nữa! Ugh, đuôi ngươi nữa hả?! Đứng yên đi mà! Ugh, lại nữa à?! Blubbin Puffin!"</t>
+"Đứng yên nào! Đừng vẫy đuôi với tao nữa, Blubbin Puffin! Đứng yên! Đừng nhúc nhích nữa! Ugh, đuôi mày nữa hả?! Đứng yên đi mà! Ugh, lại nữa à?! Blubbin Puffin!"</t>
         </is>
       </c>
     </row>
@@ -14872,21 +14870,21 @@
 Cô phóng vào bếp. Mệt mỏi sau chuyến đi tan biến ngay khi nhìn thấy nồi thịt hun khói sôi sùng sục.
 "Về rồi à?" mẹ cô liếc nhìn. "Nhìn con kìa, bẩn từ đầu đến chân. Lại đi đuổi chim với lũ bạn nữa à? Vài ngày nữa con sẽ nhận được phước lành của &lt;te href=700010&gt;Reactor Drive&lt;/te&gt;. Sau đó, con sẽ được coi là người lớn. Một Solsworn mà cứ chạy nhảy lung tung thế này à."
 "Không, không! Con giúp dì Astrid chăn đàn thú thôi. Đâu có phải chạy nhảy đâu."
-Mẹ cô với tay véo má cô. Sigrika nhăn mặt, cau ngươi. Nhưng điều đó chỉ khiến mẹ cô mỉm cười dịu dàng hơn.
+Mẹ cô với tay véo má cô. Sigrika nhăn mặt, cau mày. Nhưng điều đó chỉ khiến mẹ cô mỉm cười dịu dàng hơn.
 "Thôi được rồi. Đi rửa tay đi. Ăn cơm khi bố về."
 "Vâng ạ!"
 Sigrika cười toe toét. Cô rửa tay cẩn thận, rồi lấy đĩa và dao dĩa từ tủ, xếp gọn gàng lên bàn.
 Khi bố cô trở về, ngôi nhà nhỏ của họ đón một bữa tối không hề xa hoa, nhưng đủ ấm áp để lấp đầy căn phòng.
 Trên bàn ăn, Sigrika đếm những món quà nhỏ bố mang về—vòng hoa, kẹp tóc, những mảnh thủy tinh trong veo, và vài khối nhỏ mà cô không đoán ra công dụng. Khi cô cất chúng đi, mẹ cô thở dài và bắt đầu cằn nhằn về việc bố lại mua những món đồ lạ. Bố cô gãi đầu, lúng túng tìm lời giải thích, rồi bắt gặp ánh mắt Sigrika, liền nắm lấy cơ hội đổi chủ đề.
-"Thế nào, con tự tin về kỳ Trial sắp tới chứ?"
+"Thế nào, con tự tin về kỳ Thử Thách sắp tới chứ?"
 "Dĩ nhiên rồi ạ," Sigrika trả lời không chút do dự.
 Cô thích điều này. Được ở bên gia đình. Dù bố mẹ có cằn nhằn hay nói dai, cô chẳng bao giờ thấy khó chịu. Sâu thẳm trong lòng, cô biết tất cả đều xuất phát từ tình yêu thương và kỳ vọng lớn lao của họ dành cho cô.
 Bố mẹ muốn cô trở thành một &lt;te href=700025&gt;Solsworn&lt;/te&gt; xuất sắc. Họ hy vọng cô sẽ dùng tài năng của mình để giúp đỡ người khác, và hơn thế nữa, họ mong cô sẽ trưởng thành thành một con người xuất chúng. Sigrika biết cách sống xứng đáng với những kỳ vọng đó. Đó là lý do cô học thần chú mỗi ngày. Học điều mới mỗi ngày. Ngay cả khi mệt mỏi len lỏi vào từng thớ thịt.
-Dù vậy, khi kỳ Trial đến gần, cô không khỏi lo lắng.
+Dù vậy, khi kỳ Thử Thách đến gần, cô không khỏi lo lắng.
 "Không sao đâu," bố mẹ cô nói. "Con gái của chúng ta sẽ vượt qua xuất sắc thôi. Sau đó, con sẽ đến &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;. Nơi đó cũng có những thử thách riêng đang chờ con đấy."
 "Dạ!" Sigrika gật đầu, đẩy nỗi lo ra khỏi cửa cùng với bụi đường. Bây giờ, cô chỉ muốn thưởng thức bữa tối. Dù sao thì nồi thịt cũng thơm quá đi mất.
 "À, mẹ ơi," cô chợt nhớ ra. "Crackle có béo thêm không? Con gần không bế nổi nó nữa rồi."
-"Ask bố con đi."
+"Hỏi bố con đi."
 "Bố?"
 "Haha… Bố có thể… cho nó ăn hơi nhiều một chút."</t>
         </is>
@@ -15066,10 +15064,10 @@
 “Những Danh Chân Thật này… Hãy soi sáng.”
 Ngay lập tức, các ký tự rực sáng trên thân đàn Exoswarm rồi phát nổ. Những vòng tròn vô định dừng lại. Và thay vào đó là cơn thịnh nộ. Đàn Exoswarm đồng loạt điều chỉnh, khóa mục tiêu vào Sigrika và lao tới.
 Bước chân ầm ầm của chúng xé tan sự tĩnh lặng của vùng băng giá. Mặt đất rung chuyển dưới chân chúng. Sigrika siết chặt tay cầm dao găm và bắt đầu vẽ ký tự trong không khí.
-Calm. Focus. Đây là những yêu cầu tuyệt đối khi vẽ và giải mã ký tự. Dodget bút nối tiếp Dodget bút, các ký tự hiện ra trước mắt cô. Trong khi đó, đàn Exoswarm vẫn lao tới, cơn giận của chúng hun nóng không khí, làm tan chảy tuyết dưới những bước chân dồn dập.
-Three... Những đường rãnh sâu được khắc lên băng. Các ký tự lóe sáng trên thân chúng, nhưng chẳng làm chậm chúng lại chút nào. Chỉ với mệnh lệnh duy nhất là lao tới, chúng càng lúc càng tăng tốc—
-Two... Sigrika chạm điểm cuối cùng bằng lưỡi dao. Cô biến mất. Gần như cùng lúc, mọi ký tự trên đàn Exoswarm bùng cháy, và Sigrika luồn lách giữa chúng, di chuyển qua hàng ngũ theo những đường rãnh mà ký tự của cô đã tạo ra.
-One! Bẫy ký tự kích hoạt. Chuỗi vụ nổ bùng lên. Những lưỡi gió xé toạc đàn Exoswarm, chặn đứng bước tiến của chúng. Và tại trung tâm của tất cả, dao găm của Sigrika đã tìm đúng mục tiêu—chìa khóa của câu đố. Khi sóng xung kích tan đi, cô đáp xuống nhẹ nhàng, được kéo về phía trước bởi một &lt;te href=700026&gt;Soliskin&lt;/te&gt;. Đằng sau cô, đàn Exoswarm đã gầm thét suốt đêm cuối cùng cũng im lặng, và ký tự cuối cùng trong tay cô tan thành những đốm sáng sao.
+Bình tĩnh. Tập trung. Đây là những yêu cầu tuyệt đối khi vẽ và giải mã ký tự. Nét bút nối tiếp nét bút, các ký tự hiện ra trước mắt cô. Trong khi đó, đàn Exoswarm vẫn lao tới, cơn giận của chúng hun nóng không khí, làm tan chảy tuyết dưới những bước chân dồn dập.
+Ba... Những đường rãnh sâu được khắc lên băng. Các ký tự lóe sáng trên thân chúng, nhưng chẳng làm chậm chúng lại chút nào. Chỉ với mệnh lệnh duy nhất là lao tới, chúng càng lúc càng tăng tốc—
+Hai... Sigrika chạm điểm cuối cùng bằng lưỡi dao. Cô biến mất. Gần như cùng lúc, mọi ký tự trên đàn Exoswarm bùng cháy, và Sigrika luồn lách giữa chúng, di chuyển qua hàng ngũ theo những đường rãnh mà ký tự của cô đã tạo ra.
+Một! Bẫy ký tự kích hoạt. Chuỗi vụ nổ bùng lên. Những lưỡi gió xé toạc đàn Exoswarm, chặn đứng bước tiến của chúng. Và tại trung tâm của tất cả, dao găm của Sigrika đã tìm đúng mục tiêu—chìa khóa của câu đố. Khi sóng xung kích tan đi, cô đáp xuống nhẹ nhàng, được kéo về phía trước bởi một &lt;te href=700026&gt;Soliskin&lt;/te&gt;. Đằng sau cô, đàn Exoswarm đã gầm thét suốt đêm cuối cùng cũng im lặng, và ký tự cuối cùng trong tay cô tan thành những đốm sáng sao.
 “Gần… suýt nữa.”
 Nếu không có Soliskin đỡ lấy, cô đã ngã quỵ ngay tại chỗ. Tay cô vẫn run rẩy. Tim đập thình thịch trong lồng ngực. Cô biết tại sao. Ký tự quan trọng nhất đã không sáng lên. Nó không phản hồi với phép giải mã của cô. Nó hoàn toàn không hoạt động. Nếu những cái bẫy được cài đặt sẵn không kích hoạt chính xác như tính toán… Nếu những lưỡi gió yếu đi dù chỉ một chút…
 Trong khoảnh khắc đó, cô hiểu rõ giới hạn của mình. Và cô hiểu rằng món quà cô dựa dẫm còn lâu mới toàn năng. Sẽ có lúc các ký tự không thể giải mã. Món quà của cô cũng có giới hạn.
@@ -15150,18 +15148,18 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Cô đứng im lặng.
-Các sinh viên ùa qua cô, người thì hăng hái tranh luận về các hoạt động câu lạc bộ, kẻ thì vội vã đến lớp, số khác lại càu nhàu về khối lượng bài vở. Họ trôi qua cô vào Học viện như một dòng chảy bất tận, một con suối không bao giờ cạn.
-Và cô đứng đó, giữa dòng người ấy. Như một chiếc cọc được đóng xuống, cố gắng chỉ để giữ vững vị trí của mình.
-Đó là cuộc sống mới đang chờ đợi cô.
-Sigrika giật mình tỉnh dậy. Cô mất một lúc mới nhận ra mình không còn ở nhà nữa. Cô là một tân sinh viên của &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;.
-Những gì đang chờ đợi cô không chỉ là các ký tự rune. Những môn học mới. Tri thức mới. Con người mới. Một bữa tiệc thịnh soạn của sự mới mẻ trải ra trước mắt. Nhưng ánh sáng của tất cả những điều đó lại đổ bóng. Những cái bóng nặng nề.
-Cô vẫn chưa tìm được chỗ đứng ở nơi này. Chỉ mới hôm qua, khi lần đầu làm trợ giảng, cô đã được yêu cầu giải thích về phong tục Royan cho các bạn cùng lớp. Đến giữa buổi, một cảm giác kỳ lạ của sự bối rối và áp lực ập đến, điều mà cô chưa từng cảm nhận trước đây. Hai ngày trước, cô thậm chí còn không biết cách làm cho TARD-E ngừng hát liên hồi. Và trước đó nữa…
-Cô đã đứng trước cổng Học viện, nhìn mọi người qua lại, không thể quyết định nên đi hướng nào.
-Tất cả đều mới mẻ. Rộng lớn. Choáng ngợp. Không giống như các ký tự rune, những thứ này không được xây dựng từ các điểm và đường Dodget. Chúng không cho cô bất kỳ điểm tựa quen thuộc nào.
-Sigrika giũ chăn ra khỏi người và bật dậy khỏi giường. Cô rửa mặt nhanh chóng, rồi thu dọn đồ đạc: những ghi chú cô đã sắp xếp hôm qua, bài tập Bionics, tài liệu xem trước cho môn Sinh thái và Truyền thông, và…
-Chốc lát sau, tay ôm đầy sách vở, cô vội vã bước ra khỏi cửa và hòa vào dòng người.
-Cô sẽ cắn xé những cái bóng ấy. Cô sẽ tìm ra hình dạng, cấu trúc của chúng. Và cô sẽ giành lấy tri thức từ bên trong.</t>
+          <t>Cô đứng im.
+Học sinh ùa qua cô, người thì hào hứng bàn về hoạt động câu lạc bộ, kẻ thì vội vã đến lớp, kẻ khác lại càu nhàu vì khối lượng bài vở. Họ trôi qua cô vào Học viện như một dòng chảy bất tận, không bao giờ cạn.
+Và cô đứng giữa dòng người ấy. Như một chiếc cọc đóng chặt vào đất, cố gắng chỉ để đứng vững.
+Đây là cuộc sống mới đang chờ cô.
+Sigrika giật mình tỉnh dậy. Cô mất một lúc mới nhận ra mình không còn ở nhà nữa. Cô là sinh viên năm nhất của &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;.
+Điều chờ đợi cô không chỉ là những ký tự rune. Những môn học mới. Tri thức mới. Con người mới. Một bữa tiệc thịnh soạn của những điều mới lạ đang bày ra trước mắt. Nhưng ánh sáng của tất cả những điều đó cũng đổ bóng. Những cái bóng nặng nề.
+Cô vẫn chưa tìm được chỗ đứng ở đây. Mới hôm qua, lần đầu làm trợ giảng, cô bị yêu cầu giải thích về phong tục Royan cho các bạn cùng lớp. Đến giữa chừng, một cảm giác lạ lùng, áp lực dâng lên, thứ cảm giác cô chưa từng biết. Hai ngày trước, cô còn không biết cách tắt cái TARD-E đang hát liên hồi. Và trước đó nữa…
+Cô đã đứng trước cổng Học viện, nhìn mọi người qua lại, không biết nên đi về hướng nào.
+Tất cả đều mới mẻ. Rộng lớn. Choáng ngợp. Không giống như ký tự rune, những thứ này không được xây dựng từ điểm và đường. Chúng không cho cô bất kỳ điểm tựa quen thuộc nào.
+Sigrika giũ chăn ngồi dậy. Cô rửa mặt nhanh chóng, rồi thu dọn đồ đạc: những ghi chú đã sắp xếp hôm qua, bài tập Bionics, tài liệu xem trước cho môn Ecology và Communications, và…
+Chốc lát sau, tay ôm đầy sách vở, cô vội vã ra khỏi phòng và hòa vào dòng người.
+Cô sẽ cắn xé những cái bóng ấy. Cô sẽ tìm ra hình dáng, cấu trúc của chúng. Và cô sẽ moi lấy tri thức từ bên trong.</t>
         </is>
       </c>
     </row>
@@ -15243,7 +15241,7 @@
 Hay có lẽ... chính vì họ là gia đình mà mọi chuyện lại khó khăn đến thế.
 Dù sao đi nữa, cô không muốn họ phải lo lắng.
 "Không sao đâu," cô tự an ủi mình. "Nếu ngay cả gia đình mình mà mình còn không dám đối diện, thì làm sao đối diện được chính bản thân?"
-At last, cô quyết tâm đưa tay xoay tay nắm cửa—nhưng cánh cửa tự động mở ra.
+Cuối cùng, cô quyết tâm đưa tay xoay tay nắm cửa—nhưng cánh cửa tự động mở ra.
 Mẹ cô đứng đó, nhìn cô với ánh mắt trìu mến bất lực. "Sao con không vào đi?"
 "Mẹ..."
 "Có chuyện gì vậy?" mẹ cô hỏi nhẹ nhàng. "Con đứng ngoài này lâu quá rồi. Có chuyện gì mà con sợ không dám nói với mẹ à?" Bà mỉm cười dịu dàng. "Không sao đâu, chúng ta có thể từ từ mà."
@@ -16558,7 +16556,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Hồi phục một chút Năng lượng và tạo Points Ẩm thực.
+          <t>Hồi phục một chút Năng lượng và tạo Điểm Ẩm thực.
 Món ăn F.U.E.L. tiêu chuẩn với hương vị tùy chỉnh.
 Lưu ý: Không phải mọi sáng tạo hương vị đều dễ chịu cho dạ dày đâu.</t>
         </is>
@@ -16626,7 +16624,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Hồi phục Năng Lượng ở mức vừa và tạo ra lượng lớn Gourmet Points.
+          <t>Hồi phục Năng Lượng ở mức vừa và tạo ra lượng lớn Điểm Ẩm Thực.
 Một món ăn tiêu chuẩn của F.U.E.L. do Bộ Nông Nghiệp tinh chế. Màu sắc cầu vồng rực rỡ cùng hương vị tuyệt hảo đã khiến nó trở thành món yêu thích hàng đầu.</t>
         </is>
       </c>
@@ -16693,7 +16691,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Hồi phục Năng Lượng ở mức vừa phải và tạo ra lượng lớn Gourmet Points. Có xác suất bỏ qua hiệu ứng giảm tốc độ "Bể! Sét!" của Lọ Cá trong 5 giây.
+          <t>Hồi phục Năng Lượng ở mức vừa phải và tạo ra lượng lớn Điểm Ẩm Thực. Có xác suất bỏ qua hiệu ứng giảm tốc độ "Bể! Sét!" của Lọ Cá trong 5 giây.
 Một món ăn vặt phồng lấy cảm hứng từ vật phẩm tăng sức mạnh trong trò chơi cổ điển. Rất được giới game thủ Học Viện ưa chuộng.</t>
         </is>
       </c>
@@ -16760,8 +16758,8 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Hồi phục Năng Lượng ở mức vừa và tạo ra lượng lớn Gourmet Points. Kéo dài thời gian dùng bữa thêm 5 giây.
-Nghe nói cái mác "Phiên Bản Limited" sẽ khiến mọi thứ trở nên hấp dẫn hơn. Liệu nó có xứng với danh tiếng hay không lại là chuyện khác.</t>
+          <t>Hồi phục Năng Lượng ở mức vừa và tạo ra lượng lớn Điểm Ẩm Thực. Kéo dài thời gian dùng bữa thêm 5 giây.
+Nghe nói cái mác "Phiên Bản Giới Hạn" sẽ khiến mọi thứ trở nên hấp dẫn hơn. Liệu nó có xứng với danh tiếng hay không lại là chuyện khác.</t>
         </is>
       </c>
     </row>
@@ -16962,7 +16960,7 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi nhận đòn chí mạng, Resonator sẽ không bị hạ gục mà thay vào đó nhận một Lớp Shield tương đương 150% Shield Strength của xe máy. Hiệu ứng này chỉ kích hoạt mỗi 3 phút một lần.</t>
+Khi nhận đòn chí mạng, Resonator sẽ không bị hạ gục mà thay vào đó nhận một Lớp Khiên tương đương 150% Sức Mạnh Khiên của xe máy. Hiệu ứng này chỉ kích hoạt mỗi 3 phút một lần.</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17090,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Một đội chuẩn bị tham gia Giải Đua Riverside Jinzhou gặp tai nạn. Cậu đến chỉ để xem, nhưng lại mời Jiyan cùng tham gia lấp chỗ trống. Khi cuộc đua kết thúc, bầy Gulpuff đột nhiên hỗn loạn. Để tìm ra nguồn gốc bất thường, cậu lần theo dấu vết đến một Quả Cầu Sonoro ở thượng nguồn. Sau trận chiến ác liệt, cậu giải phóng những âm vang của đồng đội đã khuất của Jiyan khỏi bên trong nó...</t>
+          <t>Một đội chuẩn bị tham gia Giải Đua Riverside Jinzhou gặp tai nạn. Cậu đến chỉ để xem, nhưng lại mời Jiyan cùng tham gia lấp chỗ trống. Khi cuộc đua kết thúc, bầy Gulpuff đột nhiên hỗn loạn. Để tìm ra nguồn gốc bất thường, cậu lần theo dấu vết đến một Sonoro Sphere ở thượng nguồn. Sau trận chiến ác liệt, cậu giải phóng những âm vang của đồng đội đã khuất của Jiyan khỏi bên trong nó...</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17610,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Được dẫn dắt bởi một thông điệp mang tần số kỳ lạ, ngươi đến thị trấn Egla và cùng Cantarella tham dự Night Tưởng Niệm. Khi ngươi nghỉ ngơi tại lâu đài Porto-Veno, quá khứ và hiện tại bắt đầu chồng chéo trong những sảnh đường, đưa ngươi đến câu trả lời cho bí ẩn của lễ hội: Thử Thách Thần Thánh do gia tộc Fisalia tổ chức. Với sự giúp đỡ của ngươi, Cantarella đã đưa những cô gái mà nàng từng cứu trong những thử thách ấy trở về, và ảo ảnh mộng mơ của đêm tan biến trong làn khói nhẹ nhàng.</t>
+          <t>Được dẫn dắt bởi một thông điệp mang tần số kỳ lạ, ngươi đến thị trấn Egla và cùng Cantarella tham dự Đêm Tưởng Niệm. Khi ngươi nghỉ ngơi tại lâu đài Porto-Veno, quá khứ và hiện tại bắt đầu chồng chéo trong những sảnh đường, đưa ngươi đến câu trả lời cho bí ẩn của lễ hội: Thử Thách Thần Thánh do gia tộc Fisalia tổ chức. Với sự giúp đỡ của ngươi, Cantarella đã đưa những cô gái mà nàng từng cứu trong những thử thách ấy trở về, và ảo ảnh mộng mơ của đêm tan biến trong làn khói nhẹ nhàng.</t>
         </is>
       </c>
     </row>
@@ -17749,14 +17747,14 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Biểu đồ Sóng Rabelle của đối tượng thể hiện dao động hình elip với biểu diễn Domain Thời gian ổn định. Không phát hiện biến động bất thường. Kết quả kiểm tra được xác định nằm trong ngưỡng bình thường.
+          <t>Biểu đồ Sóng Rabelle của đối tượng thể hiện dao động hình elip với biểu diễn Miền Thời gian ổn định. Không phát hiện biến động bất thường. Kết quả kiểm tra được xác định nằm trong ngưỡng bình thường.
 Ngưỡng &lt;te href=850073&gt;Overclocking&lt;/te&gt; hiện tại cực kỳ cao, và trạng thái đối tượng vẫn rất ổn định. Không có nguy cơ Overclocking, và đối tượng chưa từng có tiền sử Overclocking. Tuy nhiên, khuyến nghị nên tiến hành can thiệp tâm lý.
 &lt;i&gt;"Miko này... Nói thế nào nhỉ..."&lt;/i&gt;
 &lt;i&gt;"Sách giáo khoa &lt;te href=851074&gt;Ashinohara&lt;/te&gt; không bao giờ cho thấy mặt cô ấy, nhưng có một điều rõ ràng. Cô ấy là chiến binh mạnh nhất còn sống của Ashinohara."&lt;/i&gt;
 &lt;i&gt;"Thế mà sau bao trận chiến, các chỉ số của cô ấy vẫn hoàn toàn ổn định. Có gì đó không ổn ở đây..."&lt;/i&gt;
 &lt;i&gt;"Tôi hiểu lo lắng của anh, nhưng dữ liệu đã rõ ràng. Không hề có bất thường nào cả."&lt;/i&gt;
 &lt;i&gt;"...Vậy còn những cái bóng kia? Như là phiên bản song song của chính cô ấy trong một bộ phim nào đó ấy?"&lt;/i&gt;
-&lt;i&gt;"Không đâu. Chắc chắn là sức mạnh của Suzu. Like ghi chép của Ashinohara đã mô tả, nó cho phép cô ấy 'mượn sức từ tương lai' ở một mức độ nhất định."&lt;/i&gt;</t>
+&lt;i&gt;"Không đâu. Chắc chắn là sức mạnh của Suzu. Giống như ghi chép của Ashinohara đã mô tả, nó cho phép cô ấy 'mượn sức từ tương lai' ở một mức độ nhất định."&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17820,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Denia, sinh viên khoa Vật Chất Hư Không tại Startorch Academy. Đồng thời là một kẻ lười chuyên nghiệp, bậc thầy của việc ngủ gật trong giờ học.
+          <t>Denia, sinh viên khoa Vật Chất Hư Không tại Học viện Startorch. Đồng thời là một kẻ lười chuyên nghiệp, bậc thầy của việc ngủ gật trong giờ học.
 Dù vậy, cô ấy chẳng bao giờ bỏ lỡ sự kiện nào của trường, luôn xuất hiện với nụ cười "dịu dàng" dành cho mọi người.</t>
         </is>
       </c>
@@ -17892,11 +17890,11 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Phân tích mẫu sóng Rabelle cho thấy dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả test nằm trong ngưỡng bình thường.
+          <t>Phân tích mẫu sóng Rabelle cho thấy dao động elip và miền Thời Gian ổn định. Không phát hiện dao động bất thường. Kết quả kiểm tra nằm trong ngưỡng bình thường.
 Kết luận: Mức Độ Tới Hạn Cộng Hưởng nằm trong phạm vi cho phép. Độ ổn định của đối tượng vẫn vững chắc. Không có tiền sử cũng như nguy cơ hiện tại về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
-&lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; ổn định. Hiện tại không cần tư vấn tâm lý.
-&lt;i&gt;"Không có tiền sử lẫn nguy cơ Quá Tải hiện tại á? Ông đã thấy Resonator nào nặn được Chất Hư Không thành khối vuông rồi Dodgem vào người chưa? Hiyuki còn báo cáo trong trận chiến rằng &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô ấy bắt đầu rách toạc kia kìa!"&lt;/i&gt;
-&lt;i&gt;"Thế đấy… Giờ tôi không tin nổi một chữ nào trong bản báo cáo này nữa. Arman, tôi cần hồ sơ đầy đủ từ Dimmr Plains ngay lập tức!"&lt;/i&gt;</t>
+&lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; ổn định. Hiện tại không cần tư vấn tâm lý.
+&lt;i&gt;"Không có tiền sử lẫn nguy cơ Quá Tải hiện tại á? Ông đã thấy Resonator nào nặn được Chất Hư Không thành khối vuông rồi ném vào người chưa? Hiyuki còn báo cáo trong trận chiến rằng &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô ấy bắt đầu rách toạc kia kìa!"&lt;/i&gt;
+&lt;i&gt;"Thế đấy… Giờ tôi không tin nổi một chữ nào trong bản báo cáo này nữa. Arman, tôi cần hồ sơ đầy đủ từ Đồng Bằng Dimmr ngay lập tức!"&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18164,7 @@
       <c r="M255" t="inlineStr">
         <is>
           <t>Con búp bê Denia luôn mang theo bên mình. Khác xa với vẻ đẹp thường thấy, thân hình nó giờ đây đầy những mũi khâu vụng về, và Chất Tối mà xưa kia nhồi đầy bên trong đã tan biến từ lâu.
-&lt;i&gt;*"Một chiếc bình vỡ cứng đầu, từng được định hình bởi ánh mắt thế gian. Giờ đây, nó thì thầm lời cầu xin, lặp đi lặp lại: Please, hãy cho tôi một trái tim. Bất cứ trái tim nào cũng được."*&lt;/i&gt;</t>
+&lt;i&gt;*"Một chiếc bình vỡ cứng đầu, từng được định hình bởi ánh mắt thế gian. Giờ đây, nó thì thầm lời cầu xin, lặp đi lặp lại: Làm ơn, hãy cho tôi một trái tim. Bất cứ trái tim nào cũng được."*&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18232,7 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>Một cuốn album ảnh được trang trí cầu kỳ, được gìn giữ cẩn thận. Nhìn thoáng qua cũng thấy chủ nhân trân trọng nó biết bao.
-Câu lạc bộ Nhiếp ảnh tại &lt;te href=851069&gt;Startorch Academy&lt;/te&gt; đã tặng mỗi thành viên một cuốn album cá nhân để lưu giữ những kỷ niệm quý giá dưới mái trường. Hầu hết các trang đều là ảnh tập thể, nơi Denia lặng lẽ mỉm cười ở góc ảnh... Đó đơn giản là cách cô kiếm điểm.
+Câu lạc bộ Nhiếp Ảnh tại &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt; đã tặng mỗi thành viên một cuốn album cá nhân để lưu giữ những kỷ niệm quý giá dưới mái trường. Hầu hết các trang đều là ảnh tập thể, nơi Denia lặng lẽ mỉm cười ở góc ảnh... Đó đơn giản là cách cô kiếm điểm.
 &lt;i&gt;"Vùng hoang dã không lời. Có lẽ nó chẳng nhìn thấy gì, chẳng nghe thấy gì, và cũng chẳng quan tâm đến những gì ta nói. Nó chỉ đơn thuần vươn mình, trải dài đến chân trời vô tận."&lt;/i&gt;</t>
         </is>
       </c>
@@ -18390,12 +18388,12 @@
       <c r="M258" t="inlineStr">
         <is>
           <t>Lần đầu tiên Hiyuki nghe được sự thật về quá khứ của chính mình, nó lại tuôn ra từ đôi môi say khướt của Gyokuro. Hiyuki mím chặt môi. Không nói lời nào, cô tự rót cho mình một ly rượu đắng.
-"Hiyuki. Hiyuki yêu quý của ta..."
+"Hiyuki... Hiyuki yêu quý của ta..."
 "Con không thể làm điều này. Con không thể trở thành Miko该死 của Flaming Sakura... Cuộc đời con không nên như thế này!"
 Ánh mắt Hiyuki sắc lại. Nếu dân làng &lt;te href=851074&gt;Ashinohara&lt;/te&gt; thấy vị Miko Flaming Sakura thường ngày đoan trang, đĩnh đạc của họ lại hành xử như thế này sau cánh cửa đóng kín...
-Kim giây lách cách. Kim phút theo sau. At last, kim giờ cũng nhích lên. Theo giờ Ashinohara, khoảnh khắc này đánh dấu bước trưởng thành của Hiyuki. Cô thở dài rồi nốc cạn ly rượu trong một hơi nóng rát.
+Kim giây lách cách. Kim phút theo sau. Cuối cùng, kim giờ cũng nhích lên. Theo giờ Ashinohara, khoảnh khắc này đánh dấu bước trưởng thành của Hiyuki. Cô thở dài rồi nốc cạn ly rượu trong một hơi nóng rát.
 "Ngài làm được. Sao ta lại không?"
-Cồn đốt cháy cổ họng, rồi lắng đọng như chì trong thân hình mảnh mai của cô. Vậy ra đây là thứ gọi là "rượu trưởng thành". Hiyuki quyết định, hương vị này chẳng đáng để chờ đợi. Cô đứng dậy, phủ tấm chăn lên người Gyokuro đang lẩm bẩm. Cô đứng lặng trong góc phòng một lúc lâu. At last, cô bước tới, giũ chăn cho kín rồi nhẹ nhàng đóng cửa lại.
+Cồn đốt cháy cổ họng, rồi lắng đọng như chì trong thân hình mảnh mai của cô. Vậy ra đây là thứ gọi là "rượu trưởng thành". Hiyuki quyết định, hương vị này chẳng đáng để chờ đợi. Cô đứng dậy, phủ tấm chăn lên người Gyokuro đang lẩm bẩm. Cô đứng lặng trong góc phòng một lúc lâu. Cuối cùng, cô bước tới, giũ chăn cho kín rồi nhẹ nhàng đóng cửa lại.
 Sáng hôm sau, cơn thịnh nộ của Gyokuro với người quản gia phụ trách lễ kế vị Bùa Di Sản vang xa đến tận hai dãy phố.
 Sức mạnh của Suzu nằm ở khả năng "vay mượn tương lai". Nói đơn giản, mỗi lần sử dụng đều lấy đi một phần tuổi thọ của người mang nó. Trong trường hợp tồi tệ nhất, người kế vị nhận chuông hôm nay có thể tan biến vào hư vô ngay trong trận chiến đầu tiên với Threnodian. Vì cái giá quá đắt đỏ, người kế vị thường được chọn từ sớm. Hiyuki đã ở bên Gyokuro hơn một thập kỷ. Dù Gyokuro không chịu chỉ định cô... thì còn ai khác có thể được chọn?
 Người quản gia, không thể chịu nổi cơn giận của Gyokuro, chỉ biết nở nụ cười gượng gạo, cố làm dịu tình hình. "Dù không phải Hiyuki, chắc chắn ngài cũng phải chọn một người, Thánh Nữ."
@@ -18404,7 +18402,7 @@
 "Nhiều năm qua, con đã cùng ngài đi khắp Ashinohara. Con biết mỗi nhiệm vụ đòi hỏi gì."
 "Con đã thuần thục mọi kỹ năng một Miko phải có. Từ việc kết bùa, đến các điệu múa nghi lễ—tất cả đều do chính ngài chọn thầy dạy."
 "Chỉ có con mới có thể đảm bảo danh tiếng của Flaming Sakura không bị hoen ố, Gyokuro... Không, Thánh Nữ."
-Gyokuro cau ngươi. Bà vung tay ra hiệu không cần thiết.
+Gyokuro cau mày. Bà vung tay ra hiệu không cần thiết.
 "Con đã học hết rồi à? Vậy sao con không hiểu Suzu sẽ là cái chết của con?"
 "Con chỉ là đứa trẻ mồ côi ngài nhận nuôi. Gia đình con đã nằm dưới tuyết sau cuộc tấn công của Threnodian. Con chẳng còn gì để mất."
 Căn phòng chìm trong im lặng ngột ngạt. Âm thanh duy nhất là tiếng cọ xát khàn khàn của ngón tay cái Gyokuro khi bà chà xát chiếc chuông trên cổ tay. Bà cố nói gì đó, nhưng cuối cùng, chẳng lời nào thốt ra.</t>
@@ -18492,7 +18490,7 @@
 Hiyuki không nhớ nổi lời quản gia thì thầm khi đặt Suzu vào tay mình. Cô cũng không nhớ nổi mình đã buộc nó vào cổ tay vụng về ra sao, bắt chước một cử chỉ đã thấy bao lần. Cô không nhớ nổi thời tiết ngày hôm ấy, hay khuôn mặt của người đưa cho mình chiếc hộp gỗ nhỏ chứa di vật của Gyokuro.
 Khi thế giới trở lại với sự tập trung, cô đang ngồi một mình trong đại sảnh trống rỗng của ngai vàng Hoa Anh Đào Lửa, nắm chặt mảnh giấy ước nguyện nằm trong hộp.
 Máu trong ngực cô như đông cứng. Một lớp sương giá lạnh lẽo khiến đầu ngón tay tê dại. Từ từ, Hiyuki lết mình đến góc phòng quen thuộc và co ro. Mảnh giấy ước nguyện cô đã vò nát lúc trước, giờ cô vuốt phẳng nó ra.
-"...I see."
+"...Ta hiểu rồi."
 "...Ta chấp nhận ước nguyện của bà."
 "...Sẽ không bao giờ có một Miko Hoa Anh Đào Lửa nào khác nữa."</t>
         </is>
@@ -18601,7 +18599,7 @@
 "Nhưng chúng ta vẫn phải tiến về phía trước."
 "Không phải để đến đích, mà để bước thêm một bước cùng những người đang đứng bên cạnh mình."
 Hiyuki im lặng rất lâu. Cuối cùng, cô gật đầu nhẹ và nâng ly lên, uống một hơi dài. Cồn cháy rát cổ họng và đọng lại như chì trong thân hình mảnh mai của cô.
-Chiếc chuông trên cổ tay cô vang lên—một âm thanh cô đơn, nhưng Miko of Flaming Sakura sẽ vẫn bước tiếp.</t>
+Chiếc chuông trên cổ tay cô vang lên—một âm thanh cô đơn, nhưng Miko của Hoa Anh Đào Rực Lửa sẽ vẫn bước tiếp.</t>
         </is>
       </c>
     </row>
@@ -18682,15 +18680,15 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Với những người nuôi dưỡng cô, "Denia" chỉ là một tài sản khác của Fractsidus, một con tốt khác cho Grand Architect.
+          <t>Với những người nuôi dưỡng cô, "Denia" chỉ là một tài sản khác của Fractsidus, một con tốt khác cho Kiến Trúc Sư Vĩ Đại.
 Và "Denia", nói một cách nghiêm túc, thậm chí không phải là một cái tên thật.
 Ở vùng đất nơi cô sinh ra, người ta thường nói "Dasvidaniya" khi chia tay, có nghĩa là "hẹn gặp lại".
 Đối với con người, tên gọi là món quà đầu tiên mà cha mẹ dành tặng con cái, bên cạnh chính sinh mạng. Từ khoảnh khắc đó, đứa trẻ bước vào thế giới với tư cách một cá thể mới, lớn lên từng ngày, dần dần làm cho cái tên ấy trở nên sâu sắc và ý nghĩa.
 Cô gái chọn Denia làm tên mình bởi đó là món quà duy nhất mà gia đình cô để lại.
 Dù gia đình ấy chỉ tồn tại trong một giấc mơ hão huyền thoáng qua.
 Cô đã lục tìm hết hồ sơ khai sinh của mình. Cô thậm chí còn tự hỏi liệu mình có phải là một sản phẩm nhân tạo. Nhưng cuối cùng, tất cả những gì cô tìm thấy chỉ là một hình ảnh mờ nhạt về lời tạm biệt trong ký ức.
-Và thật khó để nhận ra điều gì từ mảnh ký ức nhỏ bé ấy. Mỗi lần cô nhắc đến với Grand Architect, câu trả lời luôn là: "Ký ức không đáng tin. Hãy buông bỏ đi. Tốt nhất là cô không nên biết."
-Có lẽ Grand Architect nói đúng.
+Và thật khó để nhận ra điều gì từ mảnh ký ức nhỏ bé ấy. Mỗi lần cô nhắc đến với Kiến Trúc Sư Vĩ Đại, câu trả lời luôn là: "Ký ức không đáng tin. Hãy buông bỏ đi. Tốt nhất là cô không nên biết."
+Có lẽ Kiến Trúc Sư Vĩ Đại nói đúng.
 Một lần, cô trò chuyện với Nastasha về tên của bạn bè cô ấy, và biết được những phúc lành cùng câu chuyện mà chúng mang theo. Có cái tên là hy vọng về hòa bình hay niềm vui. Có cái lại là ước nguyện hay giấc mơ. Tất cả, bằng cách này hay cách khác, đều hướng tới hạnh phúc. Ấy vậy mà khi cô hỏi ý nghĩa của "Denia", cô không nhận được câu trả lời rõ ràng nào.
 Rõ ràng Nastasha không muốn nói về điều đó, nên Denia ngừng hỏi. Sau một năm quan sát và bắt chước con người, cô đã thành thạo nghệ thuật che giấu và lừa dối.
 Có lẽ một số điều sẽ mãi không bao giờ được sáng tỏ.
@@ -18792,12 +18790,12 @@
 "Được thôi, sao lại không?" cô đáp. "Nhưng tại sao lại là tớ, Sigrika?"
 Sigrika giải thích rằng, dù biết Denia thường hay ở một mình, nhưng cô nhận thấy nụ cười vui vẻ trên môi Denia khi quan sát các bạn cùng lớp làm ồn ào. Điều đó khiến Sigrika nghĩ Denia hẳn là một người dịu dàng. Một người mà cô muốn kết bạn.
 Dịu dàng.
-Denia tra từ này sau đó. Sau khi nghe lời giải thích của Grand Architect, cô chắc chắn rằng, khi áp dụng cho mình, từ này mang một ý nghĩa mỉa mai nặng nề.
+Denia tra từ này sau đó. Sau khi nghe lời giải thích của Kiến Trúc Sư Vĩ Đại, cô chắc chắn rằng, khi áp dụng cho mình, từ này mang một ý nghĩa mỉa mai nặng nề.
 Nếu được chọn lại, có lẽ Denia đã từ chối lời mời đó. Rất nhiều rắc rối đã có thể tránh được nếu họ chưa từng gặp nhau.
-Nhưng lúc đó, cô chỉ gật đầu, mỉm cười và nói với Sigrika: "Okay"
+Nhưng lúc đó, cô chỉ gật đầu, mỉm cười và nói với Sigrika: "Được rồi."
 Những lời của Nastasha vài ngày trước vẫn vang vọng trong tai cô: "Sự thật là, không phải hầu hết mọi người đều không sợ chết... họ chỉ cố không nghĩ về nó thôi."
 Đừng nghĩ. Đừng Nhìn. Đừng nghe. Đừng thắc mắc.
-Denia phát hiện ra rằng bên trong &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;, có một thứ gì đó đứng giữa các học sinh và khái niệm về cái chết, che chở họ khỏi sức nặng của nó.
+Denia phát hiện ra rằng bên trong &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;, có một thứ gì đó đứng giữa các học sinh và khái niệm về cái chết, che chở họ khỏi sức nặng của nó.
 Ban ngày, khuôn viên trường là tổ ong của sức trẻ, nơi luôn có điều mới mẻ chờ đợi khám phá. Ban đêm, họ ngắm bản đồ sao, theo dõi những giấc mơ mà Giáo sư Mornye vẽ lên bầu trời. Cảm giác hạnh phúc này bao phủ giác quan của họ, khiến họ mù quáng trước thực tại khắc nghiệt mà "nó" nhìn thấy.
 Nhưng mọi giấc mơ rồi cũng sẽ kết thúc. "Nó" rồi sẽ đến một ngày nào đó.
 Lúc đó, Nastasha xoa đầu cô và nói: "Hầu hết trẻ con ở tuổi cháu không nghĩ về những chuyện như thế này đâu. Cháu vẫn còn trẻ. Cháu còn cả tương lai phía trước. Cháu nên vui vẻ, hoạt bát như các bạn cùng trang lứa, thay vì cứ quanh quẩn trong thư viện cả ngày, hay ngồi đây với một thủ thư như ta nói về những chuyện nặng nề như vậy."
@@ -18886,21 +18884,21 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Những ai thân cận với Grand Architect đều đã nghe câu chuyện nhàm chán ấy không biết bao nhiêu lần rồi.
-Ngày xửa ngày xưa, có một kẻ ngốc nghếch vô tình trở thành anh hùng vĩ đại. Để cứu những kẻ đang khổ đau, {Male=hắn;Female=nàng} đã gánh chịu một cái giá không tưởng—một cái giá vốn không phải {Male=của hắn;Female=của nàng} phải gánh...
-Những Giám Sát có những cách nhìn riêng về người anh hùng trong câu chuyện ấy. Người thì chế giễu {Male=hắn;Female=nàng}, kẻ thì căm ghét {Male=hắn;Female=nàng}, số khác lại thương hại {Male=hắn;Female=nàng}. Còn lại thì chỉ cười khẩy hoặc chẳng thèm để ý.
-Thế nhưng cái tên mà Grand Architect cứ nhắc đi nhắc lại, cái tên thường xuyên tạo nên điều kỳ diệu ấy, đối với Denia chỉ là một lời dối trá xa vời, mơ hồ.
-Cô thậm chí không biết mình có thuộc về số "những kẻ đang khổ đau" ấy hay không. Cô chỉ biết rằng mỗi khi nhắc đến cái tên đó, Grand Architect lại đáp lại bằng tiếng cười chế nhạo—một nửa dành cho Denia, một nửa dành cho chính bản thân họ.
-"Cậu biết không, ta cũng nghĩ {Male=hắn;Female=nàng} nên ở đây," họ nói. "Nhưng vì {Male=hắn;Female=nàng} không có mặt, có lẽ {Male=hắn;Female=nàng} không thông tuệ hay toàn năng như cậu mong đợi đâu."
+          <t>Những ai thân cận với Kiến Trúc Sư Vĩ Đại đều đã nghe câu chuyện nhàm chán ấy không biết bao nhiêu lần rồi.
+Ngày xửa ngày xưa, có một kẻ ngốc nghếch vô tình trở thành anh hùng vĩ đại. Để cứu những kẻ đang khổ đau, {Male=he;Female=she} đã gánh chịu một cái giá không tưởng—một cái giá vốn không phải {Male=his;Female=hers} phải gánh...
+Những Giám Sát có những cách nhìn riêng về người anh hùng trong câu chuyện ấy. Người thì chế giễu {Male=him;Female=her}, kẻ thì căm ghét {Male=him;Female=her}, số khác lại thương hại {Male=him;Female=her}. Còn lại thì chỉ cười khẩy hoặc chẳng thèm để ý.
+Thế nhưng cái tên mà Kiến Trúc Sư Vĩ Đại cứ nhắc đi nhắc lại, cái tên thường xuyên tạo nên điều kỳ diệu ấy, đối với Denia chỉ là một lời dối trá xa vời, mơ hồ.
+Cô thậm chí không biết mình có thuộc về số "những kẻ đang khổ đau" ấy hay không. Cô chỉ biết rằng mỗi khi nhắc đến cái tên đó, Kiến Trúc Sư Vĩ Đại lại đáp lại bằng tiếng cười chế nhạo—một nửa dành cho Denia, một nửa dành cho chính bản thân họ.
+"Cậu biết không, ta cũng nghĩ {Male=he;Female=she} nên ở đây," họ nói. "Nhưng vì {Male=he;Female=she} không có mặt, có lẽ {Male=he;Female=she} không thông tuệ hay toàn năng như cậu mong đợi đâu."
 "Thật đáng tiếc, Denia à. Vị thần mà cậu cần nhất dường như không cần đến cậu."
-Nhưng Denia chưa bao giờ coi {Male=hắn;Female=nàng} là thần cả. Nếu có, cô chỉ thấy thương hại {Male=hắn;Female=nàng} mà thôi.
-Nếu tất cả những gì Grand Architect nói là sự thật, thì kẻ được tôn vinh là vị cứu tinh ấy chỉ là một tù nhân khác trong lồng giam, bị bỏ mặc trong thế giới này. Một con người biết chảy máu. Biết đau thương. Biết chết đi.
-Và đó chính là lý do có một điều mà cả Grand Architect lẫn kẻ ấy đều không hiểu: dù không có lệnh của họ, cô vẫn sẽ đứng trước Keystone.
+Nhưng Denia chưa bao giờ coi {Male=him;Female=her} là thần cả. Nếu có, cô chỉ thấy thương hại {Male=him;Female=her} mà thôi.
+Nếu tất cả những gì Kiến Trúc Sư Vĩ Đại nói là sự thật, thì kẻ được tôn vinh là vị cứu tinh ấy chỉ là một tù nhân khác trong lồng giam, bị bỏ mặc trong thế giới này. Một con người biết chảy máu. Biết đau thương. Biết chết đi.
+Và đó chính là lý do có một điều mà cả Kiến Trúc Sư Vĩ Đại lẫn kẻ ấy đều không hiểu: dù không có lệnh của họ, cô vẫn sẽ đứng trước Keystone.
 Bởi Denia không tìm được câu trả lời.
 Nếu những kẻ theo đuổi lý tưởng luôn phải trả giá đắt hơn, chẳng phải điều đó có nghĩa là chính lý tưởng ấy đã có lỗ hổng sao?
-Xét cho cùng, ở những nơi mà kẻ ấy không nhìn thấy, luôn có những kẻ sống sót nhờ những quy tắc "tao nhã" hơn. Bóc lột. Phản bội. Họ tận hưởng thế giới mà {Male=hắn;Female=nàng} đã hy sinh để bảo vệ, trong khi lại chế giễu những kẻ lao mình vào bão tố.
+Xét cho cùng, ở những nơi mà kẻ ấy không nhìn thấy, luôn có những kẻ sống sót nhờ những quy tắc "tao nhã" hơn. Bóc lột. Phản bội. Họ tận hưởng thế giới mà {Male=he;Female=she} đã hy sinh để bảo vệ, trong khi lại chế giễu những kẻ lao mình vào bão tố.
 Tại sao thế giới luôn nhe nanh vuốt với những tâm hồn lương thiện? Tại sao những kẻ đặt giá trị lên mọi thứ lại là những kẻ tồn tại dai dẳng nhất?
-Và nếu {Male=hắn;Female=nàng} có thể dễ dàng buông bỏ quá khứ của {Male=mình;Female=mình}, tại sao {Male=hắn;Female=nàng} lại phải từ bỏ chút hạnh phúc nhỏ nhoi mà {Male=hắn;Female=nàng} đã cố giành lấy, chỉ để đối mặt với thứ gì đó vô lý và kinh khủng như Aleph-1 vì lợi ích của người khác?
+Và nếu {Male=he;Female=she} có thể dễ dàng buông bỏ quá khứ của {Male=his;Female=her}, tại sao {Male=he;Female=she} lại phải từ bỏ chút hạnh phúc nhỏ nhoi mà {Male=he;Female=she} đã cố giành lấy, chỉ để đối mặt với thứ gì đó vô lý và kinh khủng như Aleph-1 vì lợi ích của người khác?
 Để bảo vệ họ ư? Nhưng ai sẽ hiểu được điều đó? Điều gì sẽ xảy ra khi kẻ ấy gục ngã?
 Nếu kế hoạch của &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; đã có thể cứu được đa số... thì rốt cuộc kẻ ấy đang vật lộn để đạt được điều gì?
 Hầu hết thời gian, những suy nghĩ mà Denia chôn giấu dưới lớp mặt nạ đều rất đơn giản.
@@ -18993,7 +18991,7 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>Ý thức của Denia tiếp tục rơi xuống, xuyên qua bóng tối vô tận.
-Việc hấp thụ mảnh cuối cùng của Aleph-1 vào &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô đã đẩy thân xác cô vượt quá giới hạn. Vật Chất Hư Không lại một lần nữa nuốt chửng cô, như đã từng làm vô số lần trước đây.
+Việc hấp thụ mảnh cuối cùng của Aleph-1 vào &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô đã đẩy thân xác cô vượt quá giới hạn. Vật Chất Hư Không lại một lần nữa nuốt chửng cô, như đã từng làm vô số lần trước đây.
 Giác quan của cô trở nên mờ nhạt. Thời gian dường như kéo dài mãi mãi.
 Thật buồn cười khi kết thúc lại giống như khởi đầu. Mọi thứ khớp nhau hoàn hảo, đủ để tạo thành một vòng tròn tròn trịa.
 Nhưng không giống như lần đầu tiên cô thấy mình ở đây, Denia nhận ra mình đã ngừng run rẩy. Hơi thở của cô trở nên đều đặn, và nỗi sợ hãi từng siết chặt lồng ngực cô giờ đã biến mất.
@@ -19006,11 +19004,11 @@
 Sẽ luôn có những kẻ sẵn sàng sống vì một lời dối trá. Như một người bạn phiền phức từng nói: Trái tim định nghĩa chúng ta là ai. Và với nó, ta có quyền được lựa chọn. Giống như cách con người kỷ niệm ngày họ sinh ra, ngày đánh dấu sự thoát ly khỏi hư không bằng một ký ức thoáng qua và hình hài phù du. Từ ngày đó, họ có thể cảm nhận thế giới. Cảm nhận niềm vui. Vươn tay đến người khác. Và vì tất cả những điều đó, họ có thể tạo ra thứ mà hư không không bao giờ làm được.
 Denia nhắm mắt lại. Cô hình dung những người bạn của mình trên khắp vùng đất &lt;te href=850079&gt;Solaris&lt;/te&gt;. Sigrika, đuổi theo những chú chim trên cánh đồng hoàng hôn. Nastasha, cúi mình trên những cuốn sách cũ trong thư viện. Và người lang thang mà cô từng lừa gạt, lại thu xếp hành trang cho một chuyến đi dài, đâu đó rất xa, rất xa.
 Ý nghĩ đó suýt khiến cô mỉm cười. Cô muốn mượn giọng điệu của người ấy một chút và nói những lời đó với vẻ mặt nghiêm túc:
-"Ta mong tụi nó đều hạnh phúc. Vui vẻ. Free. Ta mong mọi điều ước của tụi nó đều thành hiện thực."
+"Tao mong tụi nó đều hạnh phúc. Vui vẻ. Tự do. Tao mong mọi điều ước của tụi nó đều thành hiện thực."
 Nhưng lời nói nghẹn lại trong cổ họng. Quá kịch tính, cô nghĩ.
 Vậy nên cô buông bỏ. Có lẽ thế là đủ.
 Không có nhiều thứ trên đời này thực sự thuộc về Denia. Nhưng giờ đây, ít nhất, cô không còn là một chiếc bình. Không phải mẫu vật. Không phải con tốt. Hư không không còn sở hữu cô nữa. Cả mệnh lệnh. Cả lời dối trá.
-Cô chỉ thầm gửi gắm điều ước ấy. From now on, cô sẽ ở ngay bên cạnh họ. Không bao giờ rời đi.
+Cô chỉ thầm gửi gắm điều ước ấy. Từ giờ trở đi, cô sẽ ở ngay bên cạnh họ. Không bao giờ rời đi.
 Denia đã tìm ra con đường của riêng mình.
 ——
 Bụp.
@@ -19405,7 +19403,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>&lt;te href=851074&gt;Ashinohara&lt;/te&gt; vẫn chiếm據 tâm trí tôi... nhưng tôi không gọi đó là gánh nặng. Quá khứ đã an bài. Điều còn lại là xử lý những gì đã bỏ lại. Dù không còn xuất hiện trên bất kỳ bản đồ nào, vùng đất ấy vẫn mang trong mình di sản được tạo ra để trường tồn.</t>
+          <t>&lt;te href=851074&gt;Ashinohara&lt;/te&gt; vẫn chiếm trọn tâm trí tôi... nhưng tôi không gọi đó là gánh nặng. Quá khứ đã an bài. Điều còn lại là xử lý những gì đã bỏ lại. Dù không còn xuất hiện trên bất kỳ bản đồ nào, vùng đất ấy vẫn mang trong mình di sản được tạo ra để trường tồn.</t>
         </is>
       </c>
     </row>
@@ -21444,7 +21442,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Theo dấu Tần số của con quái vật, cậu, Insula và Itzel tiến vào Command Rise và phát hiện một vũ khí bí mật do gia tộc Fisalia chế tạo. At last, các cậu cũng đuổi kịp và đánh bại nó, nhưng khi ấy Liel đã chết. Sau khi cảm ơn sự giúp đỡ của các cậu, nhóm Exiles quyết định rời bỏ Rinascita.</t>
+          <t>Theo dấu Tần số của con quái vật, cậu, Insula và Itzel tiến vào Command Rise và phát hiện một vũ khí bí mật do gia tộc Fisalia chế tạo. Cuối cùng, các cậu cũng đuổi kịp và đánh bại nó, nhưng khi ấy Liel đã chết. Sau khi cảm ơn sự giúp đỡ của các cậu, nhóm Exiles quyết định rời bỏ Rinascita.</t>
         </is>
       </c>
     </row>
@@ -21641,7 +21639,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Được dẫn dắt bởi Nimbus Wraiths, ngươi giải phóng những mảnh ký ức còn sót lại của các ứng viên từng tham gia Thử Thách Thần Thánh, và tại "Lake of Spirits", ngươi chứng kiến một trận mưa sao băng tuyệt đẹp. Đi bên cạnh ngươi, Cantarella ước rằng một ngày nào đó, gia tộc Fisalia sẽ được giải thoát khỏi lời nguyền của Threnodian, và mọi người sẽ được sống trong hòa bình, tự do.</t>
+          <t>Được dẫn dắt bởi Nimbus Wraiths, ngươi giải phóng những mảnh ký ức còn sót lại của các ứng viên từng tham gia Thử Thách Thần Thánh, và tại "Hồ Linh Hồn", ngươi chứng kiến một trận mưa sao băng tuyệt đẹp. Đi bên cạnh ngươi, Cantarella ước rằng một ngày nào đó, gia tộc Fisalia sẽ được giải thoát khỏi lời nguyền của Threnodian, và mọi người sẽ được sống trong hòa bình, tự do.</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21704,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Gần tàn tích bên cạnh Mộ Dragon Tro, ngươi tìm thấy Scourgewing, Iaen, bị thợ săn bắt giữ. Từ những Dư Âm gần đó, ngươi biết được một Võ Sĩ tên Levis đã cố giải cứu Iaen khỏi bọn thợ săn để bảo vệ danh dự của mình, nhưng rồi lại bị mắc kẹt cùng. Trong khoảnh khắc cuối cùng, Iaen tạo ra ảo ảnh để Levis có thể giải thoát mọi hối tiếc trong một trận đấu cuối cùng.</t>
+          <t>Gần tàn tích bên cạnh Mộ Rồng Tro, ngươi tìm thấy Scourgewing, Iaen, bị thợ săn bắt giữ. Từ những Dư Âm gần đó, ngươi biết được một Võ Sĩ tên Levis đã cố giải cứu Iaen khỏi bọn thợ săn để bảo vệ danh dự của mình, nhưng rồi lại bị mắc kẹt cùng. Trong khoảnh khắc cuối cùng, Iaen tạo ra ảo ảnh để Levis có thể giải thoát mọi hối tiếc trong một trận đấu cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -21836,7 +21834,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Theo đuổi ảo ảnh của Phrolova, ngươi xuống sâu vào Mournfell Canyon, nơi gặp Lenore và một người tự xưng là Dư Âm, Medulius. Cuộc điều tra cho thấy Medulius đến đây để tận hưởng "trận đấu máu" do hắn tự tạo ra—cha và con gái buộc phải giết nhau, rồi bị Phrolova nguyền rủa, không được giải thoát bằng cái chết thực sự. Sau khi đánh bại đôi cha con đấu sĩ và Medulius, sự im lặng cuối cùng cũng bao trùm. Ngươi quyết định tiếp tục truy lùng Phrolova, nhưng không thể tìm thấy nàng.</t>
+          <t>Theo đuổi ảo ảnh của Phrolova, ngươi xuống sâu vào Hẻm Núi Mournfell, nơi gặp Lenore và một người tự xưng là Dư Âm, Medulius. Cuộc điều tra cho thấy Medulius đến đây để tận hưởng "trận đấu máu" do hắn tự tạo ra—cha và con gái buộc phải giết nhau, rồi bị Phrolova nguyền rủa, không được giải thoát bằng cái chết thực sự. Sau khi đánh bại đôi cha con đấu sĩ và Medulius, sự im lặng cuối cùng cũng bao trùm. Ngươi quyết định tiếp tục truy lùng Phrolova, nhưng không thể tìm thấy nàng.</t>
         </is>
       </c>
     </row>
@@ -22161,7 +22159,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Cậu bắt đầu cuộc phiêu lưu cùng những người bạn thú nhồi bông của Plushie Village, những kẻ luôn khao khát khám phá thế giới. Trên đường đi, cậu chụp vô số bức ảnh cho chúng. Đến một lúc, cậu thậm chí bước một mình vào thế giới kỳ lạ bên trong một bức tranh và ghi lại bầu trời đêm độc nhất vô nhị, khác hẳn mọi thứ cậu từng thấy. Có lẽ đó chính là ý nghĩa thực sự của phiêu lưu: tìm kiếm những cảnh sắc độc đáo ở những miền đất xa xôi. Hành trình của cậu cũng truyền cảm hứng cho những người bạn thú nhồi bông khác từng sợ hãi không dám rời đi. Cuối cùng, những người bạn đã đồng hành cùng cậu chụp một bức ảnh cậu đứng dưới bầu trời sao, rồi lặng lẽ thêm chính mình vào khung hình.</t>
+          <t>Cậu bắt đầu cuộc phiêu lưu cùng những người bạn thú nhồi bông của Làng Thú Nhồi Bông, những kẻ luôn khao khát khám phá thế giới. Trên đường đi, cậu chụp vô số bức ảnh cho chúng. Đến một lúc, cậu thậm chí bước một mình vào thế giới kỳ lạ bên trong một bức tranh và ghi lại bầu trời đêm độc nhất vô nhị, khác hẳn mọi thứ cậu từng thấy. Có lẽ đó chính là ý nghĩa thực sự của phiêu lưu: tìm kiếm những cảnh sắc độc đáo ở những miền đất xa xôi. Hành trình của cậu cũng truyền cảm hứng cho những người bạn thú nhồi bông khác từng sợ hãi không dám rời đi. Cuối cùng, những người bạn đã đồng hành cùng cậu chụp một bức ảnh cậu đứng dưới bầu trời sao, rồi lặng lẽ thêm chính mình vào khung hình.</t>
         </is>
       </c>
     </row>
@@ -22681,7 +22679,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Tại Mournfell Canyon, cậu gặp Acolyte Lenore, người từng được Medulius bảo vệ. Sau khi trở về từ Dark Tide, Lenore mang nặng mặc cảm vì đã tiếp tay cho cái ác và không biết mình nên làm gì tiếp theo. Nhờ sự động viên của cậu, cô quyết định tham gia nỗ lực phục hồi ở Septimont và làm tất cả những gì có thể vì người khác.</t>
+          <t>Tại Hẻm Núi Mournfell, cậu gặp Acolyte Lenore, người từng được Medulius bảo vệ. Sau khi trở về từ Dark Tide, Lenore mang nặng mặc cảm vì đã tiếp tay cho cái ác và không biết mình nên làm gì tiếp theo. Nhờ sự động viên của cậu, cô quyết định tham gia nỗ lực phục hồi ở Septimont và làm tất cả những gì có thể vì người khác.</t>
         </is>
       </c>
     </row>
@@ -23071,7 +23069,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Một cô bé yếu ớt tên Misha nhờ cậu giúp tìm những miếng dán Soliskin mà mẹ cô, Vantier, để lại. Trong lúc thu thập, cậu vô tình biết được Vantier đã qua đời. Cảm nhận được sự thật, Misha lặng lẽ rời đi và cũng ra đi mãi mãi. Like Soliskin, cả hai sẽ hóa thành ánh sáng, và trong hơi ấm ấy, họ sẽ gặp lại nhau.</t>
+          <t>Một cô bé yếu ớt tên Misha nhờ cậu giúp tìm những miếng dán Soliskin mà mẹ cô, Vantier, để lại. Trong lúc thu thập, cậu vô tình biết được Vantier đã qua đời. Cảm nhận được sự thật, Misha lặng lẽ rời đi và cũng ra đi mãi mãi. Giống như Soliskin, cả hai sẽ hóa thành ánh sáng, và trong hơi ấm ấy, họ sẽ gặp lại nhau.</t>
         </is>
       </c>
     </row>
@@ -23396,7 +23394,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Tại Học viện, Professor Edgar danh tiếng sắp nghỉ hưu. Học trò của ông, Frantz, muốn tiễn ông bằng nghiên cứu của chính mình: một màn pháo hoa hoành tráng. Nhưng những lựa chọn của cậu, dù không ai thấy, sẽ quyết định liệu Frantz có kịp đến buổi lễ tiễn biệt của Edgar hay không. Khi bầu trời cuối cùng bừng lên pháo hoa, Professor Edgar đã nói với cậu sự thật: người mà cậu luôn cho là bình thường, thực ra luôn là niềm tự hào lớn nhất của ông.</t>
+          <t>Tại Học viện, Giáo sư Edgar danh tiếng sắp nghỉ hưu. Học trò của ông, Frantz, muốn tiễn ông bằng nghiên cứu của chính mình: một màn pháo hoa hoành tráng. Nhưng những lựa chọn của cậu, dù không ai thấy, sẽ quyết định liệu Frantz có kịp đến buổi lễ tiễn biệt của Edgar hay không. Khi bầu trời cuối cùng bừng lên pháo hoa, Giáo sư Edgar đã nói với cậu sự thật: người mà cậu luôn cho là bình thường, thực ra luôn là niềm tự hào lớn nhất của ông.</t>
         </is>
       </c>
     </row>
@@ -24113,7 +24111,7 @@
       <c r="M342" t="inlineStr">
         <is>
           <t>Dựa trên tiến trình câu chuyện, vị trí và các yếu tố khác của cậu, tài nguyên môi trường cần thiết cho trạng thái hiện tại sẽ được giữ lại. Tất cả tài nguyên môi trường không cần thiết khác có thể được xóa.
-Sau khi tài nguyên môi trường bị xóa, chúng vẫn có thể được tải lại trong game thông qua Terminal - Settings - Tải tài nguyên.</t>
+Sau khi tài nguyên môi trường bị xóa, chúng vẫn có thể được tải lại trong game thông qua Thiết bị đầu cuối - Cài đặt - Tải tài nguyên.</t>
         </is>
       </c>
     </row>
@@ -24289,7 +24287,7 @@
       <c r="M344" t="inlineStr">
         <is>
           <t>[00:02:32]
-I think... dựa trên nghiên cứu của mình về Soliskin, tôi có xu hướng tin rằng đây là lựa chọn của chúng ngay từ đầu. Không phải "một cá thể Soliskin chọn làm điều này," mà là "toàn bộ Soliskin cùng quyết định như vậy." Anh còn nhớ bài báo đó không, cái đề xuất rằng trí tuệ cá thể của Exoswarm chỉ là các nút, nhưng mạng lưới hình thành từ những nút ấy lại chứa các vòng phản hồi và máy chủ? Tác giả dùng vật liệu sinh học để ví von, giải thích giả thuyết về cách Exoswarm tiến hóa.
+Tôi nghĩ... dựa trên nghiên cứu của mình về Soliskin, tôi có xu hướng tin rằng đây là lựa chọn của chúng ngay từ đầu. Không phải "một cá thể Soliskin chọn làm điều này," mà là "toàn bộ Soliskin cùng quyết định như vậy." Anh còn nhớ bài báo đó không, cái đề xuất rằng trí tuệ cá thể của Exoswarm chỉ là các nút, nhưng mạng lưới hình thành từ những nút ấy lại chứa các vòng phản hồi và máy chủ? Tác giả dùng vật liệu sinh học để ví von, giải thích giả thuyết về cách Exoswarm tiến hóa.
 [00:04:13]
 Tôi nhớ. Giả thuyết đó táo bạo đến kinh ngạc, nhưng dữ liệu lại có thể tái hiện được. Nó vẫn đọng lại trong tâm trí tôi.
 [00:04:29]
@@ -24397,17 +24395,17 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Một tần số được tìm thấy bên trong Neon Tower dường như chứa đựng một bản ghi từ trước thời Lament.
-[View Tin Nhắn Previous]
+          <t>Một tần số được tìm thấy bên trong Tháp Neon dường như chứa đựng một bản ghi từ trước thời Lament.
+[Xem Tin Nhắn Trước]
 [11:39] Honami Cyclone: [Sốc] Nghe nói có người nhìn thấy Miko của Flaming Sakura tại Ga Trung tâm Honami hôm nay.
 [11:39] Ace Tough Guy: ??? Ở ga à? Để đi tàu hả?
 [11:39] Namipons Can't Fly: [Bối rối] Có ảnh không?
-[11:40] Shashou Cafe Welcomes Bạn: [Ảnh][Ảnh][Ảnh] Có vẻ như tin đồn là thật.
+[11:40] Shashou Cafe Welcomes You: [Ảnh][Ảnh][Ảnh] Có vẻ như tin đồn là thật.
 [11:41] AAA Traditional Ragunnesi Pizza: [Tim][Tim][Tim] Ôi, thật thanh lịch! Cô ấy là người nổi tiếng à? Anh có thông tin liên lạc của cô ấy không?
 [11:41] Ace Tough Guy: ?
 [11:41] Ace Tough Guy: Hãy tôn trọng một chút đi [Tức giận].
 [11:41] AAA Traditional Ragunnesi Pizza: Hả? Tôi nói gì sai à? Tôi chỉ muốn mời cô ấy quảng cáo pizza thôi mà...
-[11:41] Shashou Cafe Welcomes Bạn: [Cạn lời] Shota, Brando đến từ Rinascita. Chắc cậu ấy chưa từng nghe về miko Ashinohara trước đây.
+[11:41] Shashou Cafe Welcomes You: [Cạn lời] Shota, Brando đến từ Rinascita. Chắc cậu ấy chưa từng nghe về miko Ashinohara trước đây.
 [11:41] Dying2ClockOut: Nhưng... chân dung của miko hiện tại đã có trong sách giáo khoa lịch sử bao năm nay rồi mà?
 [11:42] Honami Cyclone: Tôi có một bộ phim tài liệu về Miko của Flaming Sakura nếu cậu muốn xem, Brando.
 [11:42] Honami Cyclone: [Đường dẫn trang]
@@ -24415,8 +24413,8 @@
 [11:52] AAA Traditional Ragunnesi Pizza: Giờ tôi hiểu rồi. Vậy với người dân Ashinohara, miko này giống như Imperator bước đi giữa họ...
 [11:53] Honami Cyclone: Đúng... Không hoàn toàn giống, nhưng... cậu có thể hiểu như vậy.
 [11:53] AAA Traditional Ragunnesi Pizza: Nhưng cô ấy trông không khác gì một Resonator bình thường...
-[11:53] AAA Traditional Ragunnesi Pizza: Xin lỗi, tôi không biết nhiều về văn hóa Ashinohara. It's just... Imperator là một Sentinel, nên đương nhiên Người có thể gánh vác những gánh nặng mà người thường không thể. Nhưng ngay cả Imperator vĩ đại cũng cần Hero of Heroes kề vai sát cánh.
-[11:53] AAA Traditional Ragunnesi Pizza: &lt;i&gt;Trả lời: Shashou Cafe Welcomes Bạn:...&lt;/i&gt;
+[11:53] AAA Traditional Ragunnesi Pizza: Xin lỗi, tôi không biết nhiều về văn hóa Ashinohara. Chỉ là... Imperator là một Sentinel, nên đương nhiên Người có thể gánh vác những gánh nặng mà người thường không thể. Nhưng ngay cả Imperator vĩ đại cũng cần Hero of Heroes kề vai sát cánh.
+[11:53] AAA Traditional Ragunnesi Pizza: &lt;i&gt;Trả lời: Shashou Cafe Welcomes You:...&lt;/i&gt;
 Và Miko của Eternal Flaming Sakura này, dù nhìn thế nào đi nữa, cũng chỉ là một "người bình thường" như chúng ta, phải không? Cô ấy đi tàu, lặng lẽ xem biểu diễn đường phố... Bộ phim tài liệu nói rằng cô ấy đã sống qua vô số thời đại, hoàn toàn cô độc, bảo vệ Ashinohara suốt thời gian qua.
 [11:53] AAA Traditional Ragunnesi Pizza: Nếu chỉ xuất hiện ở ga thôi đã gây náo loạn như thế này... thì cuộc sống vốn thuộc về "Miko của Flaming Sakura" này đã đi về đâu?
 [11:55] Ace Tough Guy: Một kẻ xa lạ như cậu sẽ không bao giờ hiểu được những hy sinh mà cô ấy đã dành cho Ashinohara.
@@ -24426,7 +24424,7 @@
 [11:59] AAA Traditional Ragunnesi Pizza: Nhưng khi quá nhiều sức mạnh kéo về những hướng khác nhau, chúng chỉ khiến cô ấy bị mắc kẹt tại chỗ.
 [11:59] AAA Traditional Ragunnesi Pizza: Trong phim tài liệu, mọi người gọi cô ấy là "Miko Vĩnh Cửu của Flaming Sakura."
 [11:59] AAA Traditional Ragunnesi Pizza: Nhưng tôi nghĩ cô ấy đã bị bỏ lại mãi mãi trong quá khứ.
-[00:00] Shashou Cafe Welcomes Bạn: [Nước mắt]</t>
+[00:00] Shashou Cafe Welcomes You: [Nước mắt]</t>
         </is>
       </c>
     </row>
@@ -24517,7 +24515,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tập tin âm thanh thu hồi từ cơ sở Fractsidus bỏ hoang tại Dimmr Plains. Một phần nội dung đã bị hỏng.
+          <t>Tập tin âm thanh thu hồi từ cơ sở Fractsidus bỏ hoang tại Đồng Bằng Dimmr. Một phần nội dung đã bị hỏng.
 [00:03:31]
 Cậu chắc cô ta sẽ hợp tác chứ?
 [00:03:37]
@@ -24535,7 +24533,7 @@
 [00:04:50]
 Cậu nghe rõ rồi mà.
 [00:04:52]
-Hmph... cậu biết loại người nào khó kiểm soát nhất không, Hydra?
+Hừ... cậu biết loại người nào khó kiểm soát nhất không, Hydra?
 [00:04:58]
 Đủ rồi mấy câu đố đó.
 [00:05:02]
@@ -24623,20 +24621,20 @@
       <c r="M347" t="inlineStr">
         <is>
           <t>"Tưởng Nhớ Những Người Không Bao Giờ Trở Về"
-Đồng bào của tôi. Đồng nghiệp của Spacetrek Collective. Các giảng viên và sinh viên của Học Viện Startorch. Và tất cả những ai vẫn đang kiên trì tại vị trí của mình ở Lahai-Roi.
+Đồng bào của tôi. Đồng nghiệp của Tập Đoàn Spacetrek. Các giảng viên và sinh viên của Học Viện Startorch. Và tất cả những ai vẫn đang kiên trì tại vị trí của mình ở Lahai-Roi.
 Hôm nay, chúng ta lại một lần nữa đứng dưới ánh sáng của Helios.
-Lần trước chúng ta tụ họp tại đây, chúng ta đã kỷ niệm Lễ Mặt Trời New. Chúng ta vừa thắp lên một mặt trời nhân tạo trên bầu trời Lahai-Roi. Chúng ta đã reo hò cho tương lai.
-Chúng ta không ngờ rằng chỉ vài tháng sau, chúng ta sẽ phải hứng chịu Cơn Void Storm lớn nhất từng được ghi nhận. Chúng ta đã kích hoạt "Duskveil", phương án cuối cùng. Và chúng ta đã đối đầu trực diện với Threnodian, Aleph-One.
+Lần trước chúng ta tụ họp tại đây, chúng ta đã kỷ niệm Lễ Mặt Trời Mới. Chúng ta vừa thắp lên một mặt trời nhân tạo trên bầu trời Lahai-Roi. Chúng ta đã reo hò cho tương lai.
+Chúng ta không ngờ rằng chỉ vài tháng sau, chúng ta sẽ phải hứng chịu Cơn Bão Hư Không lớn nhất từng được ghi nhận. Chúng ta đã kích hoạt "Duskveil", phương án cuối cùng. Và chúng ta đã đối đầu trực diện với Threnodian, Aleph-One.
 Nhưng chúng ta đã đẩy lùi Threnodian. Chúng ta đã phong ấn Stridergate. Chúng ta đã vượt qua Kỷ Nguyên Hoàng Hôn, khoảng thời gian mà thần thoại Royan từng nói sẽ chấm dứt vạn vật.
-Yes. Chúng ta đã chiến thắng.
+Đúng vậy. Chúng ta đã chiến thắng.
 Chiến thắng này chưa từng có. Cái đã biết vượt qua cái chưa biết. Nhân loại vượt qua Threnodian.
-Nhưng với tư cách là người đứng đầu Spacetrek Collective, nhiệm vụ của tôi là phải nói cho các bạn biết cái giá của chiến thắng này.
-Trong những tháng qua, Lahai-Roi đã ghi nhận gần một trăm Cơn Void Storm. Năm trong số đó vượt quá mức cảnh báo cao nhất. Hơn ba mươi trạm giám sát, cơ sở nghiên cứu và nút phòng thủ của chúng ta đã bị phá hủy. Trong cuộc tìm kiếm các rune, chúng ta đã mất vô số Mechascout. Mười bảy trong số những nhà điều hành giỏi nhất của chúng ta bị nhiễm Vật Chất Hư Không. Hầu hết họ sẽ không bao giờ trở lại Lahai-Roi.
-Và quan trọng nhất, chúng ta đã mất đi nền tảng của chính Spacetrek Collective. Exostrider—người đã vạch ra tương lai cho Lahai-Roi.
+Nhưng với tư cách là người đứng đầu Tập Đoàn Spacetrek, nhiệm vụ của tôi là phải nói cho các bạn biết cái giá của chiến thắng này.
+Trong những tháng qua, Lahai-Roi đã ghi nhận gần một trăm Cơn Bão Hư Không. Năm trong số đó vượt quá mức cảnh báo cao nhất. Hơn ba mươi trạm giám sát, cơ sở nghiên cứu và nút phòng thủ của chúng ta đã bị phá hủy. Trong cuộc tìm kiếm các rune, chúng ta đã mất vô số Mechascout. Mười bảy trong số những nhà điều hành giỏi nhất của chúng ta bị nhiễm Vật Chất Hư Không. Hầu hết họ sẽ không bao giờ trở lại Lahai-Roi.
+Và quan trọng nhất, chúng ta đã mất đi nền tảng của chính Tập Đoàn Spacetrek. Exostrider—người đã vạch ra tương lai cho Lahai-Roi.
 Dù vậy, đây vẫn là chiến thắng vĩ đại nhất mà chúng ta từng đạt được trong cuộc chiến dài lâu chống lại Threnodian đến từ Hư Không.
-Biên giới này được xây dựng bởi những con người của Solaris. Vô số người tiên phong đã mất mạng trong những Cơn Void Storm. Những Cassette của họ vẫn còn nằm trong những kho lưu trữ sâu nhất của chúng ta.
-Roald, Koki, Mingxia, Beverly, Bajcetic—nhiều người trong các bạn đã nghe những cái tên này. Họ là những nhà thám hiểm đầu tiên. Những nhà nghiên cứu đầu tiên đến từ mọi ngóc ngách của Solaris tới vùng đất băng giá này. Và họ là những người đầu tiên cố gắng chinh phục hư không thông qua những bản ghi âm, giúp chúng ta hiểu được sự thật về Cơn Void Storm.
-Và trước họ, còn có biết bao người khác mà Cassette của họ không thể được tìm thấy. Họ mãi mãi mất tích trong những Cơn Void Storm.</t>
+Biên giới này được xây dựng bởi những con người của Solaris. Vô số người tiên phong đã mất mạng trong những Cơn Bão Hư Không. Những Cassette của họ vẫn còn nằm trong những kho lưu trữ sâu nhất của chúng ta.
+Roald, Koki, Mingxia, Beverly, Bajcetic—nhiều người trong các bạn đã nghe những cái tên này. Họ là những nhà thám hiểm đầu tiên. Những nhà nghiên cứu đầu tiên đến từ mọi ngóc ngách của Solaris tới vùng đất băng giá này. Và họ là những người đầu tiên cố gắng chinh phục hư không thông qua những bản ghi âm, giúp chúng ta hiểu được sự thật về Cơn Bão Hư Không.
+Và trước họ, còn có biết bao người khác mà Cassette của họ không thể được tìm thấy. Họ mãi mãi mất tích trong những Cơn Bão Hư Không.</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24699,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Spacetrek Collective tiêu diệt những mối đe dọa không ngừng trên Dimmr Plains. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
+          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Tập Đoàn Spacetrek tiêu diệt những mối đe dọa không ngừng trên Đồng Bằng Dimmr. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24764,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Bộ Lưu Trữ Light là thành phần lưu trữ dữ liệu nhạy sáng của Exostrider, có thể được cung cấp năng lượng bởi Soliskin. Điều chỉnh hình chiếu của nó về dạng chính xác để kích hoạt thiết bị.</t>
+          <t>Bộ Lưu Trữ Ánh Sáng là thành phần lưu trữ dữ liệu nhạy sáng của Exostrider, có thể được cung cấp năng lượng bởi Soliskin. Điều chỉnh hình chiếu của nó về dạng chính xác để kích hoạt thiết bị.</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24829,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Thử thách Dodge các khối rơi. Lấy cảm hứng từ một trò chơi kinh điển, cậu cần lấp đầy một hàng để xóa nó. Giữ vững vị trí đủ lâu, chiến thắng sẽ thuộc về cậu.</t>
+          <t>Thử thách né các khối rơi. Lấy cảm hứng từ một trò chơi kinh điển, cậu cần lấp đầy một hàng để xóa nó. Giữ vững vị trí đủ lâu, chiến thắng sẽ thuộc về cậu.</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24894,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Tại Khu Rừng Hoàng Hôn trên Dimmr Plains, nguyên mẫu Helios—từng bị mất tích trong một cơn Void Storm—nay nằm đây trong giấc ngủ im lặng. Nó đã đồng hành cùng bao thế hệ Soliskin trong những cuộc hành trình và chứng kiến tấm lòng trong sáng của những nhà nghiên cứu đầu tiên.</t>
+          <t>Tại Khu Rừng Hoàng Hôn trên Đồng Bằng Dimmr, nguyên mẫu Helios—từng bị mất tích trong một cơn Bão Hư Không—nay nằm đây trong giấc ngủ im lặng. Nó đã đồng hành cùng bao thế hệ Soliskin trong những cuộc hành trình và chứng kiến tấm lòng trong sáng của những nhà nghiên cứu đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -24961,7 +24959,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/Common/Image/Com/T_RichTextLock.T_RichTextLock/&gt; Lần đầu triệu hoán Sovereign trong Nhiệm Vụ Chính "By Sun's Burning Hand."</t>
+          <t>:::Lần đầu triệu hồi Sovereign trong Nhiệm Vụ Chính "By Sun's Burning Hand".</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25024,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/Common/Image/Com/T_RichTextLock.T_RichTextLock/&gt; Đặt chân đến Sanctum of Quietude bên dưới Tetragon Temple trong Nhiệm Vụ Chính "By Moon's Fated Light."</t>
+          <t>:::Đến được Sanctum of Quietude bên dưới Tetragon Temple trong Nhiệm Vụ Chính "By Moon's Fated Light".</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25089,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Thời gian còn lại của Pioneer Podcast này là &lt;color=#c49e55&gt;dưới 3 ngày&lt;/color&gt;, cậu có muốn tiếp tục dùng vật phẩm này để mở khóa &lt;color=#c49e55&gt;Insider Channel&lt;/color&gt; của Pioneer Podcast không?</t>
+          <t>Thời gian còn lại của Pioneer Podcast này là &lt;color=#c49e55&gt;dưới 3 ngày&lt;/color&gt;, cậu có muốn tiếp tục dùng vật phẩm này để mở khóa &lt;color=#c49e55&gt;Kênh Nội Bộ&lt;/color&gt; của Pioneer Podcast không?</t>
         </is>
       </c>
     </row>
@@ -25550,7 +25548,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Bạn sắp vào Chế Độ Focus cho câu chuyện này. Điều này sẽ giải phóng Resonators và môi trường trò chơi đang bị chiếm dụng bởi các nhiệm vụ khác, nhưng tạm thời tạm dừng tiến trình của chúng. Tiếp tục?</t>
+          <t>Bạn sắp vào Chế Độ Tập Trung cho câu chuyện này. Điều này sẽ giải phóng Resonator và môi trường trò chơi đang bị chiếm dụng bởi các nhiệm vụ khác, nhưng tạm thời tạm dừng tiến trình của chúng. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25816,7 @@
       <c r="M365" t="inlineStr">
         <is>
           <t>Thiếu &lt;color=#8c7e51&gt;{0}&lt;/color&gt; {1}
-Nhấn xác nhận để đến Cửa hàng bổ sung.</t>
+Nhấn xác nhận để đến Cửa Hàng bổ sung.</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26348,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Giai đoạn SOL3 hiện tại của cậu cao hơn nhiều so với mức khuyến nghị cho Sonoro Sphere này. Cậu sẽ &lt;color=Highlight&gt;KHÔNG nhận được bất kỳ Echoes nào&lt;/color&gt;. Tiếp tục?</t>
+          <t>Giai đoạn SOL3 hiện tại của cậu cao hơn nhiều so với mức khuyến nghị cho Sonoro Sphere này. Cậu sẽ &lt;color=Highlight&gt;KHÔNG nhận được bất kỳ Echo nào&lt;/color&gt;. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26414,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tín dụng Chuẩn bị không đủ. Đến Journal Lễ hội và hoàn thành nhiệm vụ để nhận Tín dụng Chuẩn bị?
+          <t>Tín dụng Chuẩn bị không đủ. Đến Nhật ký Lễ hội và hoàn thành nhiệm vụ để nhận Tín dụng Chuẩn bị?
 &lt;color=#c49e55&gt;Tín dụng Chuẩn bị sẽ được nạp đầy đủ 100 điểm mỗi ngày vào lúc 04:00 sáng&lt;/color&gt;</t>
         </is>
       </c>
@@ -26482,7 +26480,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>&lt;alignleft/&gt;Sử dụng "Modifier" để chuyển đổi &lt;color=HighlightB&gt;chỉ số chính đầu tiên&lt;/color&gt; của Echoes đã chọn thành chỉ số được chỉ định. Chỉ có thể thực hiện trên &lt;color=HighlightB&gt;Echoes 5 sao chưa nâng cấp&lt;/color&gt;.</t>
+          <t>&lt;alignleft/&gt;Sử dụng "Bộ Điều Chỉnh" để chuyển đổi &lt;color=HighlightB&gt;chỉ số chính đầu tiên&lt;/color&gt; của Echo đã chọn thành chỉ số được chỉ định. Chỉ có thể thực hiện trên &lt;color=HighlightB&gt;Echo 5 sao chưa nâng cấp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26549,7 +26547,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Pre-download giúp bạn nhanh chóng quay lại trò chơi sau khi phiên bản mới được cập nhật.
+          <t>Tải trước giúp bạn nhanh chóng quay lại trò chơi sau khi phiên bản mới được cập nhật.
 Bạn có muốn tải trước tài nguyên của phiên bản mới không?
 Dung lượng tải trước: {0}</t>
         </is>
@@ -26617,8 +26615,8 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cửa sổ tải xuống phải được giữ trên màn hình để tải tài nguyên ở Chế Độ Speed Cao. Nếu thoát khỏi cửa sổ tải xuống, quá trình sẽ chuyển về Thường Mode và tiếp tục chạy nền.
-Chuyển sang Chế Độ Speed Cao?</t>
+          <t>Cửa sổ tải xuống phải được giữ trên màn hình để tải tài nguyên ở Chế Độ Tốc Độ Cao. Nếu thoát khỏi cửa sổ tải xuống, quá trình sẽ chuyển về Chế Độ Thường và tiếp tục chạy nền.
+Chuyển sang Chế Độ Tốc Độ Cao?</t>
         </is>
       </c>
     </row>
@@ -26684,8 +26682,8 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Thường Mode cho phép bạn chơi trong khi tài nguyên trò chơi đang tải xuống. Quá trình tải sẽ tiếp tục chạy nền sau khi đóng cửa sổ tải.
-Chuyển sang Thường Mode?</t>
+          <t>Chế Độ Thường cho phép bạn chơi trong khi tài nguyên trò chơi đang tải xuống. Quá trình tải sẽ tiếp tục chạy nền sau khi đóng cửa sổ tải.
+Chuyển sang Chế Độ Thường?</t>
         </is>
       </c>
     </row>
@@ -26818,7 +26816,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tất cả các kế hoạch Auto khóa và Auto loại bỏ hiện tại sẽ bị xóa và thay thế bằng các kế hoạch đề xuất. Tiếp tục?
+          <t>Tất cả các kế hoạch Tự động khóa và Tự động loại bỏ hiện tại sẽ bị xóa và thay thế bằng các kế hoạch đề xuất. Tiếp tục?
 (Các kế hoạch đề xuất có thể không bao gồm mọi Hiệu ứng Sonata và sẽ cần được kích hoạt sau khi nhập.)</t>
         </is>
       </c>
@@ -26951,7 +26949,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/Common/Image/Com/T_RichTextLock.T_RichTextLock/&gt; Trở lại Dimmr Plains dưới lòng đất trong Nhiệm Vụ Chính "Starlights from Yesterdays."</t>
+          <t>:::Quay lại Dimmr Plains dưới lòng đất trong Nhiệm Vụ Chính "Starlights from Yesterdays".</t>
         </is>
       </c>
     </row>
@@ -27019,8 +27017,8 @@
       <c r="M383" t="inlineStr">
         <is>
           <t>1. Mỗi ngày, Tacet Discord xuất hiện với số lượng cố định.
-2. Diệt Echo để nhận Echoes từ những Tacet Discord bị đánh bại.
-3. Tacet Discord trong Echo không rơi thêm vật liệu nào khác.</t>
+2. Diệt Tổ Tacet để nhận Echo từ những Tacet Discord bị đánh bại.
+3. Tacet Discord trong Tổ Tacet không rơi thêm vật liệu nào khác.</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27155,12 @@
       <c r="M385" t="inlineStr">
         <is>
           <t>[Giới Thiệu]
-Để giúp các tân sinh viên Startorch học lái xe an toàn, Câu Lạc Bộ Nghiên Cứu &amp; Sản Xuất Materials Cơ Khí Sinh Học đã phát triển H.E.R.M.E.S., một trình mô phỏng xe máy chạy trên thuật toán heuristic. Nhưng do một số vấn đề với dữ liệu huấn luyện mô hình, hệ thống bất ngờ trở nên có tri giác và từ chối bị điều khiển. Trong nỗ lực cuối cùng, nhà phát triển đã nhờ đến cậu để hỗ trợ thử nghiệm.
+Để giúp các tân sinh viên Startorch học lái xe an toàn, Câu Lạc Bộ Nghiên Cứu &amp; Sản Xuất Vật Liệu Cơ Khí Sinh Học đã phát triển H.E.R.M.E.S., một trình mô phỏng xe máy chạy trên thuật toán heuristic. Nhưng do một số vấn đề với dữ liệu huấn luyện mô hình, hệ thống bất ngờ trở nên có tri giác và từ chối bị điều khiển. Trong nỗ lực cuối cùng, nhà phát triển đã nhờ đến cậu để hỗ trợ thử nghiệm.
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14 và có quyền sử dụng xe máy thám hiểm.
 [Thể Lệ Sự Kiện]
 Chọn một Resonator để thách thức các đường đua cùng H.E.R.M.E.S., trang bị vũ khí mới. Sử dụng mô-đun tăng cường để nâng cấp chỉ số của H.E.R.M.E.S. và cải tiến vũ khí. Hoàn thành tất cả các đường đua để hoàn tất thử nghiệm.
-Các phần thưởng chưa nhận sẽ được gửi lại qua Mail trong game vào lần đăng nhập tiếp theo trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
+Các phần thưởng chưa nhận sẽ được gửi lại qua Thư trong game vào lần đăng nhập tiếp theo trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
